--- a/docs/db-design_document.xlsx
+++ b/docs/db-design_document.xlsx
@@ -139,7 +139,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -168,6 +168,34 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -179,7 +207,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -263,6 +291,8 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -555,7 +585,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Ver 2.0 — 2026-05-24 更新 | 全24テーブル</t>
         </is>
@@ -1753,12 +1783,12 @@
           <t>▶ roles</t>
         </is>
       </c>
-      <c r="B4" s="26" t="n"/>
-      <c r="C4" s="26" t="n"/>
-      <c r="D4" s="26" t="n"/>
-      <c r="E4" s="26" t="n"/>
-      <c r="F4" s="26" t="n"/>
-      <c r="G4" s="26" t="n"/>
+      <c r="B4" s="29" t="n"/>
+      <c r="C4" s="29" t="n"/>
+      <c r="D4" s="29" t="n"/>
+      <c r="E4" s="29" t="n"/>
+      <c r="F4" s="29" t="n"/>
+      <c r="G4" s="30" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="12">
       <c r="A5" s="26" t="inlineStr">
@@ -1931,12 +1961,12 @@
           <t>▶ users</t>
         </is>
       </c>
-      <c r="B10" s="26" t="n"/>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="26" t="n"/>
-      <c r="G10" s="26" t="n"/>
+      <c r="B10" s="29" t="n"/>
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="29" t="n"/>
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="29" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="12">
       <c r="A11" s="26" t="inlineStr">
@@ -2369,12 +2399,12 @@
           <t>▶ pets</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n"/>
-      <c r="C24" s="26" t="n"/>
-      <c r="D24" s="26" t="n"/>
-      <c r="E24" s="26" t="n"/>
-      <c r="F24" s="26" t="n"/>
-      <c r="G24" s="26" t="n"/>
+      <c r="B24" s="29" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="29" t="n"/>
+      <c r="G24" s="30" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="12">
       <c r="A25" s="26" t="inlineStr">
@@ -2807,12 +2837,12 @@
           <t>▶ health_records</t>
         </is>
       </c>
-      <c r="B38" s="26" t="n"/>
-      <c r="C38" s="26" t="n"/>
-      <c r="D38" s="26" t="n"/>
-      <c r="E38" s="26" t="n"/>
-      <c r="F38" s="26" t="n"/>
-      <c r="G38" s="26" t="n"/>
+      <c r="B38" s="29" t="n"/>
+      <c r="C38" s="29" t="n"/>
+      <c r="D38" s="29" t="n"/>
+      <c r="E38" s="29" t="n"/>
+      <c r="F38" s="29" t="n"/>
+      <c r="G38" s="30" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="26" t="inlineStr">
@@ -3216,12 +3246,12 @@
           <t>▶ pet_care_records</t>
         </is>
       </c>
-      <c r="B51" s="26" t="n"/>
-      <c r="C51" s="26" t="n"/>
-      <c r="D51" s="26" t="n"/>
-      <c r="E51" s="26" t="n"/>
-      <c r="F51" s="26" t="n"/>
-      <c r="G51" s="26" t="n"/>
+      <c r="B51" s="29" t="n"/>
+      <c r="C51" s="29" t="n"/>
+      <c r="D51" s="29" t="n"/>
+      <c r="E51" s="29" t="n"/>
+      <c r="F51" s="29" t="n"/>
+      <c r="G51" s="30" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="26" t="inlineStr">
@@ -3489,12 +3519,12 @@
           <t>▶ symptom_checks</t>
         </is>
       </c>
-      <c r="B60" s="26" t="n"/>
-      <c r="C60" s="26" t="n"/>
-      <c r="D60" s="26" t="n"/>
-      <c r="E60" s="26" t="n"/>
-      <c r="F60" s="26" t="n"/>
-      <c r="G60" s="26" t="n"/>
+      <c r="B60" s="29" t="n"/>
+      <c r="C60" s="29" t="n"/>
+      <c r="D60" s="29" t="n"/>
+      <c r="E60" s="29" t="n"/>
+      <c r="F60" s="29" t="n"/>
+      <c r="G60" s="30" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="26" t="inlineStr">
@@ -3733,12 +3763,12 @@
           <t>▶ plans</t>
         </is>
       </c>
-      <c r="B68" s="26" t="n"/>
-      <c r="C68" s="26" t="n"/>
-      <c r="D68" s="26" t="n"/>
-      <c r="E68" s="26" t="n"/>
-      <c r="F68" s="26" t="n"/>
-      <c r="G68" s="26" t="n"/>
+      <c r="B68" s="29" t="n"/>
+      <c r="C68" s="29" t="n"/>
+      <c r="D68" s="29" t="n"/>
+      <c r="E68" s="29" t="n"/>
+      <c r="F68" s="29" t="n"/>
+      <c r="G68" s="30" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="26" t="inlineStr">
@@ -4010,12 +4040,12 @@
           <t>▶ plan_features</t>
         </is>
       </c>
-      <c r="B77" s="26" t="n"/>
-      <c r="C77" s="26" t="n"/>
-      <c r="D77" s="26" t="n"/>
-      <c r="E77" s="26" t="n"/>
-      <c r="F77" s="26" t="n"/>
-      <c r="G77" s="26" t="n"/>
+      <c r="B77" s="29" t="n"/>
+      <c r="C77" s="29" t="n"/>
+      <c r="D77" s="29" t="n"/>
+      <c r="E77" s="29" t="n"/>
+      <c r="F77" s="29" t="n"/>
+      <c r="G77" s="30" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="26" t="inlineStr">
@@ -4089,12 +4119,12 @@
           <t>▶ subscriptions</t>
         </is>
       </c>
-      <c r="B80" s="26" t="n"/>
-      <c r="C80" s="26" t="n"/>
-      <c r="D80" s="26" t="n"/>
-      <c r="E80" s="26" t="n"/>
-      <c r="F80" s="26" t="n"/>
-      <c r="G80" s="26" t="n"/>
+      <c r="B80" s="29" t="n"/>
+      <c r="C80" s="29" t="n"/>
+      <c r="D80" s="29" t="n"/>
+      <c r="E80" s="29" t="n"/>
+      <c r="F80" s="29" t="n"/>
+      <c r="G80" s="30" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="26" t="inlineStr">
@@ -4465,12 +4495,12 @@
           <t>▶ invoices</t>
         </is>
       </c>
-      <c r="B92" s="26" t="n"/>
-      <c r="C92" s="26" t="n"/>
-      <c r="D92" s="26" t="n"/>
-      <c r="E92" s="26" t="n"/>
-      <c r="F92" s="26" t="n"/>
-      <c r="G92" s="26" t="n"/>
+      <c r="B92" s="29" t="n"/>
+      <c r="C92" s="29" t="n"/>
+      <c r="D92" s="29" t="n"/>
+      <c r="E92" s="29" t="n"/>
+      <c r="F92" s="29" t="n"/>
+      <c r="G92" s="30" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="26" t="inlineStr">
@@ -4771,12 +4801,12 @@
           <t>▶ payments</t>
         </is>
       </c>
-      <c r="B102" s="26" t="n"/>
-      <c r="C102" s="26" t="n"/>
-      <c r="D102" s="26" t="n"/>
-      <c r="E102" s="26" t="n"/>
-      <c r="F102" s="26" t="n"/>
-      <c r="G102" s="26" t="n"/>
+      <c r="B102" s="29" t="n"/>
+      <c r="C102" s="29" t="n"/>
+      <c r="D102" s="29" t="n"/>
+      <c r="E102" s="29" t="n"/>
+      <c r="F102" s="29" t="n"/>
+      <c r="G102" s="30" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="26" t="inlineStr">
@@ -4982,12 +5012,12 @@
           <t>▶ appointment_slots</t>
         </is>
       </c>
-      <c r="B109" s="26" t="n"/>
-      <c r="C109" s="26" t="n"/>
-      <c r="D109" s="26" t="n"/>
-      <c r="E109" s="26" t="n"/>
-      <c r="F109" s="26" t="n"/>
-      <c r="G109" s="26" t="n"/>
+      <c r="B109" s="29" t="n"/>
+      <c r="C109" s="29" t="n"/>
+      <c r="D109" s="29" t="n"/>
+      <c r="E109" s="29" t="n"/>
+      <c r="F109" s="29" t="n"/>
+      <c r="G109" s="30" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="26" t="inlineStr">
@@ -5251,12 +5281,12 @@
           <t>▶ appointments</t>
         </is>
       </c>
-      <c r="B118" s="26" t="n"/>
-      <c r="C118" s="26" t="n"/>
-      <c r="D118" s="26" t="n"/>
-      <c r="E118" s="26" t="n"/>
-      <c r="F118" s="26" t="n"/>
-      <c r="G118" s="26" t="n"/>
+      <c r="B118" s="29" t="n"/>
+      <c r="C118" s="29" t="n"/>
+      <c r="D118" s="29" t="n"/>
+      <c r="E118" s="29" t="n"/>
+      <c r="F118" s="29" t="n"/>
+      <c r="G118" s="30" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="26" t="inlineStr">
@@ -5660,12 +5690,12 @@
           <t>▶ medical_histories</t>
         </is>
       </c>
-      <c r="B131" s="26" t="n"/>
-      <c r="C131" s="26" t="n"/>
-      <c r="D131" s="26" t="n"/>
-      <c r="E131" s="26" t="n"/>
-      <c r="F131" s="26" t="n"/>
-      <c r="G131" s="26" t="n"/>
+      <c r="B131" s="29" t="n"/>
+      <c r="C131" s="29" t="n"/>
+      <c r="D131" s="29" t="n"/>
+      <c r="E131" s="29" t="n"/>
+      <c r="F131" s="29" t="n"/>
+      <c r="G131" s="30" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="26" t="inlineStr">
@@ -6073,12 +6103,12 @@
           <t>▶ medical_attachments</t>
         </is>
       </c>
-      <c r="B144" s="26" t="n"/>
-      <c r="C144" s="26" t="n"/>
-      <c r="D144" s="26" t="n"/>
-      <c r="E144" s="26" t="n"/>
-      <c r="F144" s="26" t="n"/>
-      <c r="G144" s="26" t="n"/>
+      <c r="B144" s="29" t="n"/>
+      <c r="C144" s="29" t="n"/>
+      <c r="D144" s="29" t="n"/>
+      <c r="E144" s="29" t="n"/>
+      <c r="F144" s="29" t="n"/>
+      <c r="G144" s="30" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="26" t="inlineStr">
@@ -6251,12 +6281,12 @@
           <t>▶ consult_chat_messages</t>
         </is>
       </c>
-      <c r="B150" s="26" t="n"/>
-      <c r="C150" s="26" t="n"/>
-      <c r="D150" s="26" t="n"/>
-      <c r="E150" s="26" t="n"/>
-      <c r="F150" s="26" t="n"/>
-      <c r="G150" s="26" t="n"/>
+      <c r="B150" s="29" t="n"/>
+      <c r="C150" s="29" t="n"/>
+      <c r="D150" s="29" t="n"/>
+      <c r="E150" s="29" t="n"/>
+      <c r="F150" s="29" t="n"/>
+      <c r="G150" s="30" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="26" t="inlineStr">
@@ -6454,12 +6484,12 @@
           <t>▶ notifications</t>
         </is>
       </c>
-      <c r="B157" s="26" t="n"/>
-      <c r="C157" s="26" t="n"/>
-      <c r="D157" s="26" t="n"/>
-      <c r="E157" s="26" t="n"/>
-      <c r="F157" s="26" t="n"/>
-      <c r="G157" s="26" t="n"/>
+      <c r="B157" s="29" t="n"/>
+      <c r="C157" s="29" t="n"/>
+      <c r="D157" s="29" t="n"/>
+      <c r="E157" s="29" t="n"/>
+      <c r="F157" s="29" t="n"/>
+      <c r="G157" s="30" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="26" t="inlineStr">
@@ -6628,12 +6658,12 @@
           <t>▶ notification_recipients</t>
         </is>
       </c>
-      <c r="B163" s="26" t="n"/>
-      <c r="C163" s="26" t="n"/>
-      <c r="D163" s="26" t="n"/>
-      <c r="E163" s="26" t="n"/>
-      <c r="F163" s="26" t="n"/>
-      <c r="G163" s="26" t="n"/>
+      <c r="B163" s="29" t="n"/>
+      <c r="C163" s="29" t="n"/>
+      <c r="D163" s="29" t="n"/>
+      <c r="E163" s="29" t="n"/>
+      <c r="F163" s="29" t="n"/>
+      <c r="G163" s="30" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="26" t="inlineStr">
@@ -6773,12 +6803,12 @@
           <t>▶ email_templates</t>
         </is>
       </c>
-      <c r="B168" s="26" t="n"/>
-      <c r="C168" s="26" t="n"/>
-      <c r="D168" s="26" t="n"/>
-      <c r="E168" s="26" t="n"/>
-      <c r="F168" s="26" t="n"/>
-      <c r="G168" s="26" t="n"/>
+      <c r="B168" s="29" t="n"/>
+      <c r="C168" s="29" t="n"/>
+      <c r="D168" s="29" t="n"/>
+      <c r="E168" s="29" t="n"/>
+      <c r="F168" s="29" t="n"/>
+      <c r="G168" s="30" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="26" t="inlineStr">
@@ -6980,12 +7010,12 @@
           <t>▶ email_messages</t>
         </is>
       </c>
-      <c r="B175" s="26" t="n"/>
-      <c r="C175" s="26" t="n"/>
-      <c r="D175" s="26" t="n"/>
-      <c r="E175" s="26" t="n"/>
-      <c r="F175" s="26" t="n"/>
-      <c r="G175" s="26" t="n"/>
+      <c r="B175" s="29" t="n"/>
+      <c r="C175" s="29" t="n"/>
+      <c r="D175" s="29" t="n"/>
+      <c r="E175" s="29" t="n"/>
+      <c r="F175" s="29" t="n"/>
+      <c r="G175" s="30" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="26" t="inlineStr">
@@ -7253,12 +7283,12 @@
           <t>▶ pet_calendar_marks</t>
         </is>
       </c>
-      <c r="B184" s="26" t="n"/>
-      <c r="C184" s="26" t="n"/>
-      <c r="D184" s="26" t="n"/>
-      <c r="E184" s="26" t="n"/>
-      <c r="F184" s="26" t="n"/>
-      <c r="G184" s="26" t="n"/>
+      <c r="B184" s="29" t="n"/>
+      <c r="C184" s="29" t="n"/>
+      <c r="D184" s="29" t="n"/>
+      <c r="E184" s="29" t="n"/>
+      <c r="F184" s="29" t="n"/>
+      <c r="G184" s="30" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="26" t="inlineStr">
@@ -7530,12 +7560,12 @@
           <t>▶ dismissed_reminders</t>
         </is>
       </c>
-      <c r="B193" s="26" t="n"/>
-      <c r="C193" s="26" t="n"/>
-      <c r="D193" s="26" t="n"/>
-      <c r="E193" s="26" t="n"/>
-      <c r="F193" s="26" t="n"/>
-      <c r="G193" s="26" t="n"/>
+      <c r="B193" s="29" t="n"/>
+      <c r="C193" s="29" t="n"/>
+      <c r="D193" s="29" t="n"/>
+      <c r="E193" s="29" t="n"/>
+      <c r="F193" s="29" t="n"/>
+      <c r="G193" s="30" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="26" t="inlineStr">
@@ -7679,12 +7709,12 @@
           <t>▶ announcements</t>
         </is>
       </c>
-      <c r="B198" s="26" t="n"/>
-      <c r="C198" s="26" t="n"/>
-      <c r="D198" s="26" t="n"/>
-      <c r="E198" s="26" t="n"/>
-      <c r="F198" s="26" t="n"/>
-      <c r="G198" s="26" t="n"/>
+      <c r="B198" s="29" t="n"/>
+      <c r="C198" s="29" t="n"/>
+      <c r="D198" s="29" t="n"/>
+      <c r="E198" s="29" t="n"/>
+      <c r="F198" s="29" t="n"/>
+      <c r="G198" s="30" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="26" t="inlineStr">
@@ -7919,12 +7949,12 @@
           <t>▶ password_reset_tokens</t>
         </is>
       </c>
-      <c r="B206" s="26" t="n"/>
-      <c r="C206" s="26" t="n"/>
-      <c r="D206" s="26" t="n"/>
-      <c r="E206" s="26" t="n"/>
-      <c r="F206" s="26" t="n"/>
-      <c r="G206" s="26" t="n"/>
+      <c r="B206" s="29" t="n"/>
+      <c r="C206" s="29" t="n"/>
+      <c r="D206" s="29" t="n"/>
+      <c r="E206" s="29" t="n"/>
+      <c r="F206" s="29" t="n"/>
+      <c r="G206" s="30" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="26" t="inlineStr">
@@ -8216,10 +8246,10 @@
           <t>── Auth（認証） ──</t>
         </is>
       </c>
-      <c r="B4" s="26" t="n"/>
-      <c r="C4" s="26" t="n"/>
-      <c r="D4" s="26" t="n"/>
-      <c r="E4" s="26" t="n"/>
+      <c r="B4" s="29" t="n"/>
+      <c r="C4" s="29" t="n"/>
+      <c r="D4" s="29" t="n"/>
+      <c r="E4" s="30" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="12">
       <c r="A5" s="26" t="inlineStr">
@@ -8335,10 +8365,10 @@
           <t>── ペット・健康管理 ──</t>
         </is>
       </c>
-      <c r="B9" s="26" t="n"/>
-      <c r="C9" s="26" t="n"/>
-      <c r="D9" s="26" t="n"/>
-      <c r="E9" s="26" t="n"/>
+      <c r="B9" s="29" t="n"/>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="30" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="12">
       <c r="A10" s="26" t="inlineStr">
@@ -8481,10 +8511,10 @@
           <t>── プラン・課金 ──</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n"/>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="26" t="n"/>
-      <c r="E15" s="26" t="n"/>
+      <c r="B15" s="29" t="n"/>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="30" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="26" t="inlineStr">
@@ -8681,10 +8711,10 @@
           <t>── 予約・診療記録 ──</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n"/>
-      <c r="C23" s="26" t="n"/>
-      <c r="D23" s="26" t="n"/>
-      <c r="E23" s="26" t="n"/>
+      <c r="B23" s="29" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="30" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="26" t="inlineStr">
@@ -8908,10 +8938,10 @@
           <t>── メッセージング・通知 ──</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n"/>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="26" t="n"/>
+      <c r="B32" s="29" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="30" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="26" t="inlineStr">
@@ -9108,10 +9138,10 @@
           <t>── UX補助 ──</t>
         </is>
       </c>
-      <c r="B40" s="26" t="n"/>
-      <c r="C40" s="26" t="n"/>
-      <c r="D40" s="26" t="n"/>
-      <c r="E40" s="26" t="n"/>
+      <c r="B40" s="29" t="n"/>
+      <c r="C40" s="29" t="n"/>
+      <c r="D40" s="29" t="n"/>
+      <c r="E40" s="30" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="26" t="inlineStr">
@@ -9574,51 +9604,51 @@
     <row r="22" ht="15" customHeight="1" s="12">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>admin@petlifeplus.local</t>
+          <t>super@petlife.local</t>
         </is>
       </c>
       <c r="B22" s="26" t="inlineStr">
         <is>
-          <t>admin123</t>
+          <t>super123</t>
         </is>
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SUPER</t>
         </is>
       </c>
       <c r="D22" s="26" t="inlineStr">
         <is>
-          <t>管理者</t>
+          <t>開発者（全権限）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="12">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>owner1@petlifeplus.local</t>
+          <t>admin@petlife.local</t>
         </is>
       </c>
       <c r="B23" s="26" t="inlineStr">
         <is>
-          <t>user123</t>
+          <t>admin123</t>
         </is>
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>USER</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="D23" s="26" t="inlineStr">
         <is>
-          <t>一般ユーザー（プレミアム）</t>
+          <t>管理者</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="12">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>vet1@petlifeplus.local</t>
+          <t>vet1@petlife.local</t>
         </is>
       </c>
       <c r="B24" s="26" t="inlineStr">
@@ -9640,7 +9670,7 @@
     <row r="25" ht="15" customHeight="1" s="12">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>staff1@petlifeplus.local</t>
+          <t>staff1@petlife.local</t>
         </is>
       </c>
       <c r="B25" s="26" t="inlineStr">
@@ -9662,7 +9692,7 @@
     <row r="26" ht="15" customHeight="1" s="12">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>owner2@petlifeplus.local</t>
+          <t>owner1@petlife.local</t>
         </is>
       </c>
       <c r="B26" s="26" t="inlineStr">
@@ -9677,19 +9707,19 @@
       </c>
       <c r="D26" s="26" t="inlineStr">
         <is>
-          <t>一般ユーザー（スタンダード）</t>
+          <t>一般ユーザー（ライト）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="12">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>owner.light@petlifeplus.local</t>
+          <t>owner2@petlife.local</t>
         </is>
       </c>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t>light123</t>
+          <t>user123</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
@@ -9699,19 +9729,19 @@
       </c>
       <c r="D27" s="26" t="inlineStr">
         <is>
-          <t>ライトプランユーザー</t>
+          <t>一般ユーザー（スタンダード）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="12">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>owner.standard@petlifeplus.local</t>
+          <t>owner3@petlife.local</t>
         </is>
       </c>
       <c r="B28" s="26" t="inlineStr">
         <is>
-          <t>standard123</t>
+          <t>user123</t>
         </is>
       </c>
       <c r="C28" s="26" t="inlineStr">
@@ -9721,31 +9751,15 @@
       </c>
       <c r="D28" s="26" t="inlineStr">
         <is>
-          <t>スタンダードプランユーザー</t>
+          <t>一般ユーザー（プレミアム）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="12">
-      <c r="A29" s="26" t="inlineStr">
-        <is>
-          <t>owner.premium@petlifeplus.local</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="inlineStr">
-        <is>
-          <t>premium123</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>USER</t>
-        </is>
-      </c>
-      <c r="D29" s="26" t="inlineStr">
-        <is>
-          <t>プレミアムプランユーザー</t>
-        </is>
-      </c>
+      <c r="A29" s="26" t="inlineStr"/>
+      <c r="B29" s="26" t="inlineStr"/>
+      <c r="C29" s="26" t="inlineStr"/>
+      <c r="D29" s="26" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="12"/>
     <row r="31" ht="15" customHeight="1" s="12"/>
@@ -9787,7 +9801,7 @@
       </c>
       <c r="C34" s="26" t="inlineStr">
         <is>
-          <t>各ユーザーの飼いペット（犬・猫）</t>
+          <t>ポチ/タロウ/レオン/ピーコ/カレン/ボス（すべて犬）</t>
         </is>
       </c>
       <c r="D34" s="26" t="inlineStr"/>
@@ -9805,7 +9819,7 @@
       </c>
       <c r="C35" s="26" t="inlineStr">
         <is>
-          <t>ペット1〜3の健康記録</t>
+          <t>ペット1～3の健康記録</t>
         </is>
       </c>
       <c r="D35" s="26" t="inlineStr"/>
@@ -9823,7 +9837,7 @@
       </c>
       <c r="C36" s="26" t="inlineStr">
         <is>
-          <t>ペット1〜3のケア記録</t>
+          <t>ポチのケア記録（3件）</t>
         </is>
       </c>
       <c r="D36" s="26" t="inlineStr"/>
@@ -9841,7 +9855,7 @@
       </c>
       <c r="C37" s="26" t="inlineStr">
         <is>
-          <t>各プランへの契約</t>
+          <t>owner1→ポチ(STANDARD)、owner2→レオン(STANDARD)、owner1→ピーコ(LIGHT)、owner2→カレン(STANDARD)、owner3→ボス(PREMIUM)</t>
         </is>
       </c>
       <c r="D37" s="26" t="inlineStr"/>

--- a/docs/db-design_document.xlsx
+++ b/docs/db-design_document.xlsx
@@ -1719,7 +1719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G212"/>
+  <dimension ref="A1:G216"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.4921875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="18" min="1" max="1"/>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="B63" s="26" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>requested_by_user_id</t>
         </is>
       </c>
       <c r="C63" s="26" t="inlineStr">
@@ -3617,7 +3617,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E63" s="26" t="inlineStr"/>
+      <c r="E63" s="26" t="n"/>
       <c r="F63" s="26" t="inlineStr">
         <is>
           <t>FK → users.id</t>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="G63" s="26" t="inlineStr">
         <is>
-          <t>ユーザーID</t>
+          <t>依頼者ユーザーID</t>
         </is>
       </c>
     </row>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B64" s="26" t="inlineStr">
         <is>
-          <t>symptoms</t>
+          <t>symptom_type</t>
         </is>
       </c>
       <c r="C64" s="26" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D64" s="26" t="inlineStr">
@@ -3650,11 +3650,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E64" s="26" t="inlineStr"/>
-      <c r="F64" s="26" t="inlineStr"/>
+      <c r="E64" s="26" t="n"/>
+      <c r="F64" s="26" t="n"/>
       <c r="G64" s="26" t="inlineStr">
         <is>
-          <t>症状テキスト</t>
+          <t>症状種別</t>
         </is>
       </c>
     </row>
@@ -3666,12 +3666,12 @@
       </c>
       <c r="B65" s="26" t="inlineStr">
         <is>
-          <t>ai_response</t>
+          <t>onset_text</t>
         </is>
       </c>
       <c r="C65" s="26" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D65" s="26" t="inlineStr">
@@ -3684,10 +3684,10 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="F65" s="26" t="inlineStr"/>
+      <c r="F65" s="26" t="n"/>
       <c r="G65" s="26" t="inlineStr">
         <is>
-          <t>AI 回答</t>
+          <t>発症状況テキスト</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="B66" s="26" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>memo</t>
         </is>
       </c>
       <c r="C66" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="D66" s="26" t="inlineStr">
@@ -3717,10 +3717,10 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="F66" s="26" t="inlineStr"/>
+      <c r="F66" s="26" t="n"/>
       <c r="G66" s="26" t="inlineStr">
         <is>
-          <t>重症度</t>
+          <t>補足メモ</t>
         </is>
       </c>
     </row>
@@ -3732,208 +3732,203 @@
       </c>
       <c r="B67" s="26" t="inlineStr">
         <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="D67" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E67" s="26" t="n"/>
+      <c r="F67" s="26" t="inlineStr">
+        <is>
+          <t>CHECK IN (LOW/MEDIUM/HIGH)</t>
+        </is>
+      </c>
+      <c r="G67" s="26" t="inlineStr">
+        <is>
+          <t>重症度</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>symptom_checks</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>CHECK IN (OBSERVE/CONSULT/VISIT)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>推奨対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>symptom_checks</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>guidance</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>AIガイダンス本文</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>symptom_checks</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ai_model</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>使用AIモデル名</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>symptom_checks</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>deleted_at</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>論理削除日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>symptom_checks</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C67" s="26" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="D67" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E67" s="26" t="inlineStr">
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
         <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="F67" s="26" t="inlineStr"/>
-      <c r="G67" s="26" t="inlineStr">
-        <is>
-          <t>作成日時</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="27" t="inlineStr">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>作成日時（更新なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="27" t="inlineStr">
         <is>
           <t>▶ plans</t>
         </is>
       </c>
-      <c r="B68" s="29" t="n"/>
-      <c r="C68" s="29" t="n"/>
-      <c r="D68" s="29" t="n"/>
-      <c r="E68" s="29" t="n"/>
-      <c r="F68" s="29" t="n"/>
-      <c r="G68" s="30" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="26" t="inlineStr">
-        <is>
-          <t>plans</t>
-        </is>
-      </c>
-      <c r="B69" s="26" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C69" s="26" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D69" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E69" s="26" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="F69" s="26" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G69" s="26" t="inlineStr">
-        <is>
-          <t>プランID</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="26" t="inlineStr">
-        <is>
-          <t>plans</t>
-        </is>
-      </c>
-      <c r="B70" s="26" t="inlineStr">
-        <is>
-          <t>plan_code</t>
-        </is>
-      </c>
-      <c r="C70" s="26" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D70" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E70" s="26" t="inlineStr"/>
-      <c r="F70" s="26" t="inlineStr">
-        <is>
-          <t>UNIQUE</t>
-        </is>
-      </c>
-      <c r="G70" s="26" t="inlineStr">
-        <is>
-          <t>プランコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="26" t="inlineStr">
-        <is>
-          <t>plans</t>
-        </is>
-      </c>
-      <c r="B71" s="26" t="inlineStr">
-        <is>
-          <t>plan_name</t>
-        </is>
-      </c>
-      <c r="C71" s="26" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="D71" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E71" s="26" t="inlineStr"/>
-      <c r="F71" s="26" t="inlineStr"/>
-      <c r="G71" s="26" t="inlineStr">
-        <is>
-          <t>プラン名</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="26" t="inlineStr">
-        <is>
-          <t>plans</t>
-        </is>
-      </c>
-      <c r="B72" s="26" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="C72" s="26" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D72" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E72" s="26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F72" s="26" t="inlineStr"/>
-      <c r="G72" s="26" t="inlineStr">
-        <is>
-          <t>月額料金（円）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="26" t="inlineStr">
-        <is>
-          <t>plans</t>
-        </is>
-      </c>
-      <c r="B73" s="26" t="inlineStr">
-        <is>
-          <t>features_json</t>
-        </is>
-      </c>
-      <c r="C73" s="26" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D73" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E73" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F73" s="26" t="inlineStr"/>
-      <c r="G73" s="26" t="inlineStr">
-        <is>
-          <t>機能一覧JSON（表示用）</t>
-        </is>
-      </c>
+      <c r="B73" s="29" t="n"/>
+      <c r="C73" s="29" t="n"/>
+      <c r="D73" s="29" t="n"/>
+      <c r="E73" s="29" t="n"/>
+      <c r="F73" s="29" t="n"/>
+      <c r="G73" s="30" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="26" t="inlineStr">
@@ -3943,28 +3938,32 @@
       </c>
       <c r="B74" s="26" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C74" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D74" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E74" s="26" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F74" s="26" t="inlineStr"/>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F74" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G74" s="26" t="inlineStr">
         <is>
-          <t>論理削除日時</t>
+          <t>プランID</t>
         </is>
       </c>
     </row>
@@ -3976,12 +3975,12 @@
       </c>
       <c r="B75" s="26" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>plan_code</t>
         </is>
       </c>
       <c r="C75" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="D75" s="26" t="inlineStr">
@@ -3989,15 +3988,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E75" s="26" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="F75" s="26" t="inlineStr"/>
+      <c r="E75" s="26" t="inlineStr"/>
+      <c r="F75" s="26" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
       <c r="G75" s="26" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>プランコード</t>
         </is>
       </c>
     </row>
@@ -4009,12 +4008,12 @@
       </c>
       <c r="B76" s="26" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>plan_name</t>
         </is>
       </c>
       <c r="C76" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D76" s="26" t="inlineStr">
@@ -4022,124 +4021,160 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E76" s="26" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="E76" s="26" t="inlineStr"/>
       <c r="F76" s="26" t="inlineStr"/>
       <c r="G76" s="26" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>プラン名</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="27" t="inlineStr">
-        <is>
-          <t>▶ plan_features</t>
-        </is>
-      </c>
-      <c r="B77" s="29" t="n"/>
-      <c r="C77" s="29" t="n"/>
-      <c r="D77" s="29" t="n"/>
-      <c r="E77" s="29" t="n"/>
-      <c r="F77" s="29" t="n"/>
-      <c r="G77" s="30" t="n"/>
+      <c r="A77" s="26" t="inlineStr">
+        <is>
+          <t>plans</t>
+        </is>
+      </c>
+      <c r="B77" s="26" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="C77" s="26" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D77" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E77" s="26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F77" s="26" t="inlineStr"/>
+      <c r="G77" s="26" t="inlineStr">
+        <is>
+          <t>月額料金（円）</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="26" t="inlineStr">
         <is>
-          <t>plan_features</t>
+          <t>plans</t>
         </is>
       </c>
       <c r="B78" s="26" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>features_json</t>
         </is>
       </c>
       <c r="C78" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D78" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E78" s="26" t="inlineStr"/>
-      <c r="F78" s="26" t="inlineStr">
-        <is>
-          <t>PK, FK → plans.id</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E78" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F78" s="26" t="inlineStr"/>
       <c r="G78" s="26" t="inlineStr">
         <is>
-          <t>プランID</t>
+          <t>機能一覧JSON（表示用）</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="26" t="inlineStr">
         <is>
-          <t>plan_features</t>
+          <t>plans</t>
         </is>
       </c>
       <c r="B79" s="26" t="inlineStr">
         <is>
-          <t>feature_code</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C79" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D79" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E79" s="26" t="inlineStr"/>
-      <c r="F79" s="26" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E79" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F79" s="26" t="inlineStr"/>
       <c r="G79" s="26" t="inlineStr">
         <is>
-          <t>機能コード</t>
+          <t>論理削除日時</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="27" t="inlineStr">
-        <is>
-          <t>▶ subscriptions</t>
-        </is>
-      </c>
-      <c r="B80" s="29" t="n"/>
-      <c r="C80" s="29" t="n"/>
-      <c r="D80" s="29" t="n"/>
-      <c r="E80" s="29" t="n"/>
-      <c r="F80" s="29" t="n"/>
-      <c r="G80" s="30" t="n"/>
+      <c r="A80" s="26" t="inlineStr">
+        <is>
+          <t>plans</t>
+        </is>
+      </c>
+      <c r="B80" s="26" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C80" s="26" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D80" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E80" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="F80" s="26" t="inlineStr"/>
+      <c r="G80" s="26" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="26" t="inlineStr">
         <is>
-          <t>subscriptions</t>
+          <t>plans</t>
         </is>
       </c>
       <c r="B81" s="26" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C81" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D81" s="26" t="inlineStr">
@@ -4149,62 +4184,38 @@
       </c>
       <c r="E81" s="26" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="F81" s="26" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="F81" s="26" t="inlineStr"/>
       <c r="G81" s="26" t="inlineStr">
         <is>
-          <t>サブスクID</t>
+          <t>更新日時</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="26" t="inlineStr">
-        <is>
-          <t>subscriptions</t>
-        </is>
-      </c>
-      <c r="B82" s="26" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="C82" s="26" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D82" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E82" s="26" t="inlineStr"/>
-      <c r="F82" s="26" t="inlineStr">
-        <is>
-          <t>FK → users.id</t>
-        </is>
-      </c>
-      <c r="G82" s="26" t="inlineStr">
-        <is>
-          <t>ユーザーID</t>
-        </is>
-      </c>
+      <c r="A82" s="27" t="inlineStr">
+        <is>
+          <t>▶ plan_features</t>
+        </is>
+      </c>
+      <c r="B82" s="29" t="n"/>
+      <c r="C82" s="29" t="n"/>
+      <c r="D82" s="29" t="n"/>
+      <c r="E82" s="29" t="n"/>
+      <c r="F82" s="29" t="n"/>
+      <c r="G82" s="30" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="26" t="inlineStr">
         <is>
-          <t>subscriptions</t>
+          <t>plan_features</t>
         </is>
       </c>
       <c r="B83" s="26" t="inlineStr">
         <is>
-          <t>pet_id</t>
+          <t>plan_id</t>
         </is>
       </c>
       <c r="C83" s="26" t="inlineStr">
@@ -4220,29 +4231,29 @@
       <c r="E83" s="26" t="inlineStr"/>
       <c r="F83" s="26" t="inlineStr">
         <is>
-          <t>FK → pets.id</t>
+          <t>PK, FK → plans.id</t>
         </is>
       </c>
       <c r="G83" s="26" t="inlineStr">
         <is>
-          <t>ペットID</t>
+          <t>プランID</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="26" t="inlineStr">
         <is>
-          <t>subscriptions</t>
+          <t>plan_features</t>
         </is>
       </c>
       <c r="B84" s="26" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>feature_code</t>
         </is>
       </c>
       <c r="C84" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="D84" s="26" t="inlineStr">
@@ -4253,47 +4264,27 @@
       <c r="E84" s="26" t="inlineStr"/>
       <c r="F84" s="26" t="inlineStr">
         <is>
-          <t>FK → plans.id</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G84" s="26" t="inlineStr">
         <is>
-          <t>プランID</t>
+          <t>機能コード</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="26" t="inlineStr">
-        <is>
-          <t>subscriptions</t>
-        </is>
-      </c>
-      <c r="B85" s="26" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C85" s="26" t="inlineStr">
-        <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="D85" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E85" s="26" t="inlineStr">
-        <is>
-          <t>'ACTIVE'</t>
-        </is>
-      </c>
-      <c r="F85" s="26" t="inlineStr"/>
-      <c r="G85" s="26" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>▶ subscriptions</t>
+        </is>
+      </c>
+      <c r="B85" s="29" t="n"/>
+      <c r="C85" s="29" t="n"/>
+      <c r="D85" s="29" t="n"/>
+      <c r="E85" s="29" t="n"/>
+      <c r="F85" s="29" t="n"/>
+      <c r="G85" s="30" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="26" t="inlineStr">
@@ -4303,12 +4294,12 @@
       </c>
       <c r="B86" s="26" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C86" s="26" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D86" s="26" t="inlineStr">
@@ -4316,11 +4307,19 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E86" s="26" t="inlineStr"/>
-      <c r="F86" s="26" t="inlineStr"/>
+      <c r="E86" s="26" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F86" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G86" s="26" t="inlineStr">
         <is>
-          <t>開始日</t>
+          <t>サブスクID</t>
         </is>
       </c>
     </row>
@@ -4332,28 +4331,28 @@
       </c>
       <c r="B87" s="26" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C87" s="26" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D87" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E87" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F87" s="26" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E87" s="26" t="inlineStr"/>
+      <c r="F87" s="26" t="inlineStr">
+        <is>
+          <t>FK → users.id</t>
+        </is>
+      </c>
       <c r="G87" s="26" t="inlineStr">
         <is>
-          <t>終了日</t>
+          <t>ユーザーID</t>
         </is>
       </c>
     </row>
@@ -4365,28 +4364,28 @@
       </c>
       <c r="B88" s="26" t="inlineStr">
         <is>
-          <t>renewal_date</t>
+          <t>pet_id</t>
         </is>
       </c>
       <c r="C88" s="26" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D88" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E88" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F88" s="26" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E88" s="26" t="inlineStr"/>
+      <c r="F88" s="26" t="inlineStr">
+        <is>
+          <t>FK → pets.id</t>
+        </is>
+      </c>
       <c r="G88" s="26" t="inlineStr">
         <is>
-          <t>更新日</t>
+          <t>ペットID</t>
         </is>
       </c>
     </row>
@@ -4398,28 +4397,28 @@
       </c>
       <c r="B89" s="26" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>plan_id</t>
         </is>
       </c>
       <c r="C89" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D89" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E89" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F89" s="26" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E89" s="26" t="inlineStr"/>
+      <c r="F89" s="26" t="inlineStr">
+        <is>
+          <t>FK → plans.id</t>
+        </is>
+      </c>
       <c r="G89" s="26" t="inlineStr">
         <is>
-          <t>論理削除日時</t>
+          <t>プランID</t>
         </is>
       </c>
     </row>
@@ -4431,12 +4430,12 @@
       </c>
       <c r="B90" s="26" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C90" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D90" s="26" t="inlineStr">
@@ -4446,13 +4445,13 @@
       </c>
       <c r="E90" s="26" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
+          <t>'ACTIVE'</t>
         </is>
       </c>
       <c r="F90" s="26" t="inlineStr"/>
       <c r="G90" s="26" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>状態</t>
         </is>
       </c>
     </row>
@@ -4464,12 +4463,12 @@
       </c>
       <c r="B91" s="26" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>start_date</t>
         </is>
       </c>
       <c r="C91" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D91" s="26" t="inlineStr">
@@ -4477,115 +4476,127 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E91" s="26" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="E91" s="26" t="inlineStr"/>
       <c r="F91" s="26" t="inlineStr"/>
       <c r="G91" s="26" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>開始日</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="27" t="inlineStr">
-        <is>
-          <t>▶ invoices</t>
-        </is>
-      </c>
-      <c r="B92" s="29" t="n"/>
-      <c r="C92" s="29" t="n"/>
-      <c r="D92" s="29" t="n"/>
-      <c r="E92" s="29" t="n"/>
-      <c r="F92" s="29" t="n"/>
-      <c r="G92" s="30" t="n"/>
+      <c r="A92" s="26" t="inlineStr">
+        <is>
+          <t>subscriptions</t>
+        </is>
+      </c>
+      <c r="B92" s="26" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="C92" s="26" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D92" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E92" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F92" s="26" t="inlineStr"/>
+      <c r="G92" s="26" t="inlineStr">
+        <is>
+          <t>終了日</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="26" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>subscriptions</t>
         </is>
       </c>
       <c r="B93" s="26" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>renewal_date</t>
         </is>
       </c>
       <c r="C93" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D93" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E93" s="26" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="F93" s="26" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F93" s="26" t="inlineStr"/>
       <c r="G93" s="26" t="inlineStr">
         <is>
-          <t>請求書ID</t>
+          <t>更新日</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="26" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>subscriptions</t>
         </is>
       </c>
       <c r="B94" s="26" t="inlineStr">
         <is>
-          <t>subscription_id</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C94" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D94" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E94" s="26" t="inlineStr"/>
-      <c r="F94" s="26" t="inlineStr">
-        <is>
-          <t>FK → subscriptions.id</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E94" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F94" s="26" t="inlineStr"/>
       <c r="G94" s="26" t="inlineStr">
         <is>
-          <t>サブスクID</t>
+          <t>論理削除日時</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="26" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>subscriptions</t>
         </is>
       </c>
       <c r="B95" s="26" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C95" s="26" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D95" s="26" t="inlineStr">
@@ -4593,28 +4604,32 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E95" s="26" t="inlineStr"/>
+      <c r="E95" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="F95" s="26" t="inlineStr"/>
       <c r="G95" s="26" t="inlineStr">
         <is>
-          <t>金額（円）</t>
+          <t>作成日時</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="26" t="inlineStr">
         <is>
-          <t>invoices</t>
+          <t>subscriptions</t>
         </is>
       </c>
       <c r="B96" s="26" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C96" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D96" s="26" t="inlineStr">
@@ -4624,44 +4639,28 @@
       </c>
       <c r="E96" s="26" t="inlineStr">
         <is>
-          <t>'UNPAID'</t>
+          <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
       <c r="F96" s="26" t="inlineStr"/>
       <c r="G96" s="26" t="inlineStr">
         <is>
-          <t>状態</t>
+          <t>更新日時</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="26" t="inlineStr">
-        <is>
-          <t>invoices</t>
-        </is>
-      </c>
-      <c r="B97" s="26" t="inlineStr">
-        <is>
-          <t>due_date</t>
-        </is>
-      </c>
-      <c r="C97" s="26" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="D97" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E97" s="26" t="inlineStr"/>
-      <c r="F97" s="26" t="inlineStr"/>
-      <c r="G97" s="26" t="inlineStr">
-        <is>
-          <t>支払期限</t>
-        </is>
-      </c>
+      <c r="A97" s="27" t="inlineStr">
+        <is>
+          <t>▶ invoices</t>
+        </is>
+      </c>
+      <c r="B97" s="29" t="n"/>
+      <c r="C97" s="29" t="n"/>
+      <c r="D97" s="29" t="n"/>
+      <c r="E97" s="29" t="n"/>
+      <c r="F97" s="29" t="n"/>
+      <c r="G97" s="30" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="26" t="inlineStr">
@@ -4671,28 +4670,32 @@
       </c>
       <c r="B98" s="26" t="inlineStr">
         <is>
-          <t>paid_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C98" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D98" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E98" s="26" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F98" s="26" t="inlineStr"/>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F98" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G98" s="26" t="inlineStr">
         <is>
-          <t>支払日時</t>
+          <t>請求書ID</t>
         </is>
       </c>
     </row>
@@ -4704,28 +4707,28 @@
       </c>
       <c r="B99" s="26" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>subscription_id</t>
         </is>
       </c>
       <c r="C99" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D99" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E99" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F99" s="26" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E99" s="26" t="inlineStr"/>
+      <c r="F99" s="26" t="inlineStr">
+        <is>
+          <t>FK → subscriptions.id</t>
+        </is>
+      </c>
       <c r="G99" s="26" t="inlineStr">
         <is>
-          <t>論理削除日時</t>
+          <t>サブスクID</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4740,12 @@
       </c>
       <c r="B100" s="26" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C100" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D100" s="26" t="inlineStr">
@@ -4750,15 +4753,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E100" s="26" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="E100" s="26" t="inlineStr"/>
       <c r="F100" s="26" t="inlineStr"/>
       <c r="G100" s="26" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>金額（円）</t>
         </is>
       </c>
     </row>
@@ -4770,12 +4769,12 @@
       </c>
       <c r="B101" s="26" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C101" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D101" s="26" t="inlineStr">
@@ -4785,113 +4784,125 @@
       </c>
       <c r="E101" s="26" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
+          <t>'UNPAID'</t>
         </is>
       </c>
       <c r="F101" s="26" t="inlineStr"/>
       <c r="G101" s="26" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>状態</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="27" t="inlineStr">
-        <is>
-          <t>▶ payments</t>
-        </is>
-      </c>
-      <c r="B102" s="29" t="n"/>
-      <c r="C102" s="29" t="n"/>
-      <c r="D102" s="29" t="n"/>
-      <c r="E102" s="29" t="n"/>
-      <c r="F102" s="29" t="n"/>
-      <c r="G102" s="30" t="n"/>
+      <c r="A102" s="26" t="inlineStr">
+        <is>
+          <t>invoices</t>
+        </is>
+      </c>
+      <c r="B102" s="26" t="inlineStr">
+        <is>
+          <t>due_date</t>
+        </is>
+      </c>
+      <c r="C102" s="26" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D102" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E102" s="26" t="inlineStr"/>
+      <c r="F102" s="26" t="inlineStr"/>
+      <c r="G102" s="26" t="inlineStr">
+        <is>
+          <t>支払期限</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="26" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>invoices</t>
         </is>
       </c>
       <c r="B103" s="26" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>paid_at</t>
         </is>
       </c>
       <c r="C103" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D103" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E103" s="26" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="F103" s="26" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F103" s="26" t="inlineStr"/>
       <c r="G103" s="26" t="inlineStr">
         <is>
-          <t>支払ID</t>
+          <t>支払日時</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="26" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>invoices</t>
         </is>
       </c>
       <c r="B104" s="26" t="inlineStr">
         <is>
-          <t>invoice_id</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C104" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D104" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E104" s="26" t="inlineStr"/>
-      <c r="F104" s="26" t="inlineStr">
-        <is>
-          <t>FK → invoices.id</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E104" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F104" s="26" t="inlineStr"/>
       <c r="G104" s="26" t="inlineStr">
         <is>
-          <t>請求書ID</t>
+          <t>論理削除日時</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="26" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>invoices</t>
         </is>
       </c>
       <c r="B105" s="26" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C105" s="26" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D105" s="26" t="inlineStr">
@@ -4899,79 +4910,63 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E105" s="26" t="inlineStr"/>
+      <c r="E105" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="F105" s="26" t="inlineStr"/>
       <c r="G105" s="26" t="inlineStr">
         <is>
-          <t>支払金額（円）</t>
+          <t>作成日時</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="26" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>invoices</t>
         </is>
       </c>
       <c r="B106" s="26" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C106" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D106" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E106" s="26" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
       <c r="F106" s="26" t="inlineStr"/>
       <c r="G106" s="26" t="inlineStr">
         <is>
-          <t>支払方法</t>
+          <t>更新日時</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="26" t="inlineStr">
-        <is>
-          <t>payments</t>
-        </is>
-      </c>
-      <c r="B107" s="26" t="inlineStr">
-        <is>
-          <t>paid_at</t>
-        </is>
-      </c>
-      <c r="C107" s="26" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D107" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E107" s="26" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="F107" s="26" t="inlineStr"/>
-      <c r="G107" s="26" t="inlineStr">
-        <is>
-          <t>支払日時</t>
-        </is>
-      </c>
+      <c r="A107" s="27" t="inlineStr">
+        <is>
+          <t>▶ payments</t>
+        </is>
+      </c>
+      <c r="B107" s="29" t="n"/>
+      <c r="C107" s="29" t="n"/>
+      <c r="D107" s="29" t="n"/>
+      <c r="E107" s="29" t="n"/>
+      <c r="F107" s="29" t="n"/>
+      <c r="G107" s="30" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="26" t="inlineStr">
@@ -4981,12 +4976,12 @@
       </c>
       <c r="B108" s="26" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C108" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D108" s="26" t="inlineStr">
@@ -4996,43 +4991,67 @@
       </c>
       <c r="E108" s="26" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="F108" s="26" t="inlineStr"/>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F108" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G108" s="26" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>支払ID</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="27" t="inlineStr">
-        <is>
-          <t>▶ appointment_slots</t>
-        </is>
-      </c>
-      <c r="B109" s="29" t="n"/>
-      <c r="C109" s="29" t="n"/>
-      <c r="D109" s="29" t="n"/>
-      <c r="E109" s="29" t="n"/>
-      <c r="F109" s="29" t="n"/>
-      <c r="G109" s="30" t="n"/>
+      <c r="A109" s="26" t="inlineStr">
+        <is>
+          <t>payments</t>
+        </is>
+      </c>
+      <c r="B109" s="26" t="inlineStr">
+        <is>
+          <t>invoice_id</t>
+        </is>
+      </c>
+      <c r="C109" s="26" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D109" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E109" s="26" t="inlineStr"/>
+      <c r="F109" s="26" t="inlineStr">
+        <is>
+          <t>FK → invoices.id</t>
+        </is>
+      </c>
+      <c r="G109" s="26" t="inlineStr">
+        <is>
+          <t>請求書ID</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="26" t="inlineStr">
         <is>
-          <t>appointment_slots</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="B110" s="26" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C110" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D110" s="26" t="inlineStr">
@@ -5040,65 +5059,61 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E110" s="26" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="F110" s="26" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="E110" s="26" t="inlineStr"/>
+      <c r="F110" s="26" t="inlineStr"/>
       <c r="G110" s="26" t="inlineStr">
         <is>
-          <t>枠ID</t>
+          <t>支払金額（円）</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="26" t="inlineStr">
         <is>
-          <t>appointment_slots</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="B111" s="26" t="inlineStr">
         <is>
-          <t>slot_date</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C111" s="26" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="D111" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E111" s="26" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E111" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="F111" s="26" t="inlineStr"/>
       <c r="G111" s="26" t="inlineStr">
         <is>
-          <t>予約日</t>
+          <t>支払方法</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="26" t="inlineStr">
         <is>
-          <t>appointment_slots</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="B112" s="26" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>paid_at</t>
         </is>
       </c>
       <c r="C112" s="26" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D112" s="26" t="inlineStr">
@@ -5106,28 +5121,32 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E112" s="26" t="inlineStr"/>
+      <c r="E112" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="F112" s="26" t="inlineStr"/>
       <c r="G112" s="26" t="inlineStr">
         <is>
-          <t>開始時刻</t>
+          <t>支払日時</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="26" t="inlineStr">
         <is>
-          <t>appointment_slots</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="B113" s="26" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C113" s="26" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D113" s="26" t="inlineStr">
@@ -5135,46 +5154,30 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E113" s="26" t="inlineStr"/>
+      <c r="E113" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="F113" s="26" t="inlineStr"/>
       <c r="G113" s="26" t="inlineStr">
         <is>
-          <t>終了時刻</t>
+          <t>作成日時</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="26" t="inlineStr">
-        <is>
-          <t>appointment_slots</t>
-        </is>
-      </c>
-      <c r="B114" s="26" t="inlineStr">
-        <is>
-          <t>max_count</t>
-        </is>
-      </c>
-      <c r="C114" s="26" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D114" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E114" s="26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F114" s="26" t="inlineStr"/>
-      <c r="G114" s="26" t="inlineStr">
-        <is>
-          <t>最大受付数</t>
-        </is>
-      </c>
+      <c r="A114" s="27" t="inlineStr">
+        <is>
+          <t>▶ appointment_slots</t>
+        </is>
+      </c>
+      <c r="B114" s="29" t="n"/>
+      <c r="C114" s="29" t="n"/>
+      <c r="D114" s="29" t="n"/>
+      <c r="E114" s="29" t="n"/>
+      <c r="F114" s="29" t="n"/>
+      <c r="G114" s="30" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="26" t="inlineStr">
@@ -5184,28 +5187,32 @@
       </c>
       <c r="B115" s="26" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C115" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D115" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E115" s="26" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F115" s="26" t="inlineStr"/>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F115" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G115" s="26" t="inlineStr">
         <is>
-          <t>論理削除日時</t>
+          <t>予約枠ID</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5224,7 @@
       </c>
       <c r="B116" s="26" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>slot_datetime</t>
         </is>
       </c>
       <c r="C116" s="26" t="inlineStr">
@@ -5230,15 +5237,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E116" s="26" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="F116" s="26" t="inlineStr"/>
+      <c r="E116" s="26" t="n"/>
+      <c r="F116" s="26" t="n"/>
       <c r="G116" s="26" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>予約枠日時</t>
         </is>
       </c>
     </row>
@@ -5250,53 +5253,73 @@
       </c>
       <c r="B117" s="26" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C117" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="D117" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E117" s="26" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="F117" s="26" t="inlineStr"/>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F117" s="26" t="n"/>
       <c r="G117" s="26" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="27" t="inlineStr">
-        <is>
-          <t>▶ appointments</t>
-        </is>
-      </c>
-      <c r="B118" s="29" t="n"/>
-      <c r="C118" s="29" t="n"/>
-      <c r="D118" s="29" t="n"/>
-      <c r="E118" s="29" t="n"/>
-      <c r="F118" s="29" t="n"/>
-      <c r="G118" s="30" t="n"/>
+      <c r="A118" s="26" t="inlineStr">
+        <is>
+          <t>appointment_slots</t>
+        </is>
+      </c>
+      <c r="B118" s="26" t="inlineStr">
+        <is>
+          <t>is_blocked</t>
+        </is>
+      </c>
+      <c r="C118" s="26" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D118" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E118" s="26" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F118" s="26" t="n"/>
+      <c r="G118" s="26" t="inlineStr">
+        <is>
+          <t>true=ブロック枠 / false=追加枠</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="26" t="inlineStr">
         <is>
-          <t>appointments</t>
+          <t>appointment_slots</t>
         </is>
       </c>
       <c r="B119" s="26" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_by_user_id</t>
         </is>
       </c>
       <c r="C119" s="26" t="inlineStr">
@@ -5309,69 +5332,65 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E119" s="26" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
+      <c r="E119" s="26" t="n"/>
       <c r="F119" s="26" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>FK → users.id</t>
         </is>
       </c>
       <c r="G119" s="26" t="inlineStr">
         <is>
-          <t>予約ID</t>
+          <t>作成者ユーザーID</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="26" t="inlineStr">
         <is>
-          <t>appointments</t>
+          <t>appointment_slots</t>
         </is>
       </c>
       <c r="B120" s="26" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C120" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D120" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E120" s="26" t="inlineStr"/>
-      <c r="F120" s="26" t="inlineStr">
-        <is>
-          <t>FK → users.id</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E120" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F120" s="26" t="n"/>
       <c r="G120" s="26" t="inlineStr">
         <is>
-          <t>ユーザーID</t>
+          <t>論理削除日時</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="26" t="inlineStr">
         <is>
-          <t>appointments</t>
+          <t>appointment_slots</t>
         </is>
       </c>
       <c r="B121" s="26" t="inlineStr">
         <is>
-          <t>pet_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C121" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D121" s="26" t="inlineStr">
@@ -5379,54 +5398,30 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E121" s="26" t="inlineStr"/>
-      <c r="F121" s="26" t="inlineStr">
-        <is>
-          <t>FK → pets.id</t>
-        </is>
-      </c>
+      <c r="E121" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="F121" s="26" t="n"/>
       <c r="G121" s="26" t="inlineStr">
         <is>
-          <t>ペットID</t>
+          <t>作成日時（更新なし）</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="26" t="inlineStr">
-        <is>
-          <t>appointments</t>
-        </is>
-      </c>
-      <c r="B122" s="26" t="inlineStr">
-        <is>
-          <t>slot_id</t>
-        </is>
-      </c>
-      <c r="C122" s="26" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D122" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E122" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F122" s="26" t="inlineStr">
-        <is>
-          <t>FK → appointment_slots.id</t>
-        </is>
-      </c>
-      <c r="G122" s="26" t="inlineStr">
-        <is>
-          <t>枠ID</t>
-        </is>
-      </c>
+      <c r="A122" s="27" t="inlineStr">
+        <is>
+          <t>▶ appointments</t>
+        </is>
+      </c>
+      <c r="B122" s="29" t="n"/>
+      <c r="C122" s="29" t="n"/>
+      <c r="D122" s="29" t="n"/>
+      <c r="E122" s="29" t="n"/>
+      <c r="F122" s="29" t="n"/>
+      <c r="G122" s="30" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="26" t="inlineStr">
@@ -5436,12 +5431,12 @@
       </c>
       <c r="B123" s="26" t="inlineStr">
         <is>
-          <t>appointment_date</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C123" s="26" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D123" s="26" t="inlineStr">
@@ -5449,11 +5444,19 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E123" s="26" t="inlineStr"/>
-      <c r="F123" s="26" t="inlineStr"/>
+      <c r="E123" s="26" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F123" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G123" s="26" t="inlineStr">
         <is>
-          <t>予約日</t>
+          <t>予約ID</t>
         </is>
       </c>
     </row>
@@ -5465,12 +5468,12 @@
       </c>
       <c r="B124" s="26" t="inlineStr">
         <is>
-          <t>appointment_time</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C124" s="26" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D124" s="26" t="inlineStr">
@@ -5479,10 +5482,14 @@
         </is>
       </c>
       <c r="E124" s="26" t="inlineStr"/>
-      <c r="F124" s="26" t="inlineStr"/>
+      <c r="F124" s="26" t="inlineStr">
+        <is>
+          <t>FK → users.id</t>
+        </is>
+      </c>
       <c r="G124" s="26" t="inlineStr">
         <is>
-          <t>予約時刻</t>
+          <t>ユーザーID</t>
         </is>
       </c>
     </row>
@@ -5494,28 +5501,28 @@
       </c>
       <c r="B125" s="26" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>pet_id</t>
         </is>
       </c>
       <c r="C125" s="26" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D125" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E125" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F125" s="26" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E125" s="26" t="inlineStr"/>
+      <c r="F125" s="26" t="inlineStr">
+        <is>
+          <t>FK → pets.id</t>
+        </is>
+      </c>
       <c r="G125" s="26" t="inlineStr">
         <is>
-          <t>受診理由</t>
+          <t>ペットID</t>
         </is>
       </c>
     </row>
@@ -5527,28 +5534,32 @@
       </c>
       <c r="B126" s="26" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>slot_id</t>
         </is>
       </c>
       <c r="C126" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D126" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E126" s="26" t="inlineStr">
         <is>
-          <t>'PENDING'</t>
-        </is>
-      </c>
-      <c r="F126" s="26" t="inlineStr"/>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F126" s="26" t="inlineStr">
+        <is>
+          <t>FK → appointment_slots.id</t>
+        </is>
+      </c>
       <c r="G126" s="26" t="inlineStr">
         <is>
-          <t>状態</t>
+          <t>枠ID</t>
         </is>
       </c>
     </row>
@@ -5560,28 +5571,24 @@
       </c>
       <c r="B127" s="26" t="inlineStr">
         <is>
-          <t>zoom_join_url</t>
+          <t>appointment_date</t>
         </is>
       </c>
       <c r="C127" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D127" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E127" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E127" s="26" t="inlineStr"/>
       <c r="F127" s="26" t="inlineStr"/>
       <c r="G127" s="26" t="inlineStr">
         <is>
-          <t>Zoom 参加URL</t>
+          <t>予約日</t>
         </is>
       </c>
     </row>
@@ -5593,28 +5600,24 @@
       </c>
       <c r="B128" s="26" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>appointment_time</t>
         </is>
       </c>
       <c r="C128" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D128" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E128" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E128" s="26" t="inlineStr"/>
       <c r="F128" s="26" t="inlineStr"/>
       <c r="G128" s="26" t="inlineStr">
         <is>
-          <t>論理削除日時</t>
+          <t>予約時刻</t>
         </is>
       </c>
     </row>
@@ -5626,28 +5629,28 @@
       </c>
       <c r="B129" s="26" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="C129" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D129" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E129" s="26" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="F129" s="26" t="inlineStr"/>
       <c r="G129" s="26" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>受診理由</t>
         </is>
       </c>
     </row>
@@ -5659,12 +5662,12 @@
       </c>
       <c r="B130" s="26" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C130" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D130" s="26" t="inlineStr">
@@ -5674,117 +5677,129 @@
       </c>
       <c r="E130" s="26" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
+          <t>'PENDING'</t>
         </is>
       </c>
       <c r="F130" s="26" t="inlineStr"/>
       <c r="G130" s="26" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>状態</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="27" t="inlineStr">
-        <is>
-          <t>▶ medical_histories</t>
-        </is>
-      </c>
-      <c r="B131" s="29" t="n"/>
-      <c r="C131" s="29" t="n"/>
-      <c r="D131" s="29" t="n"/>
-      <c r="E131" s="29" t="n"/>
-      <c r="F131" s="29" t="n"/>
-      <c r="G131" s="30" t="n"/>
+      <c r="A131" s="26" t="inlineStr">
+        <is>
+          <t>appointments</t>
+        </is>
+      </c>
+      <c r="B131" s="26" t="inlineStr">
+        <is>
+          <t>zoom_join_url</t>
+        </is>
+      </c>
+      <c r="C131" s="26" t="inlineStr">
+        <is>
+          <t>VARCHAR(500)</t>
+        </is>
+      </c>
+      <c r="D131" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E131" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F131" s="26" t="inlineStr"/>
+      <c r="G131" s="26" t="inlineStr">
+        <is>
+          <t>Zoom 参加URL</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="26" t="inlineStr">
         <is>
-          <t>medical_histories</t>
+          <t>appointments</t>
         </is>
       </c>
       <c r="B132" s="26" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C132" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D132" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E132" s="26" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="F132" s="26" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F132" s="26" t="inlineStr"/>
       <c r="G132" s="26" t="inlineStr">
         <is>
-          <t>診療記録ID</t>
+          <t>論理削除日時</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="26" t="inlineStr">
         <is>
-          <t>medical_histories</t>
+          <t>appointments</t>
         </is>
       </c>
       <c r="B133" s="26" t="inlineStr">
         <is>
-          <t>appointment_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C133" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D133" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E133" s="26" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F133" s="26" t="inlineStr">
-        <is>
-          <t>FK → appointments.id UNIQUE</t>
-        </is>
-      </c>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="F133" s="26" t="inlineStr"/>
       <c r="G133" s="26" t="inlineStr">
         <is>
-          <t>予約ID</t>
+          <t>作成日時</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="26" t="inlineStr">
         <is>
-          <t>medical_histories</t>
+          <t>appointments</t>
         </is>
       </c>
       <c r="B134" s="26" t="inlineStr">
         <is>
-          <t>pet_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C134" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D134" s="26" t="inlineStr">
@@ -5792,50 +5807,30 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E134" s="26" t="inlineStr"/>
-      <c r="F134" s="26" t="inlineStr">
-        <is>
-          <t>FK → pets.id</t>
-        </is>
-      </c>
+      <c r="E134" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="F134" s="26" t="inlineStr"/>
       <c r="G134" s="26" t="inlineStr">
         <is>
-          <t>ペットID</t>
+          <t>更新日時</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="26" t="inlineStr">
-        <is>
-          <t>medical_histories</t>
-        </is>
-      </c>
-      <c r="B135" s="26" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="C135" s="26" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D135" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E135" s="26" t="inlineStr"/>
-      <c r="F135" s="26" t="inlineStr">
-        <is>
-          <t>FK → users.id</t>
-        </is>
-      </c>
-      <c r="G135" s="26" t="inlineStr">
-        <is>
-          <t>担当獣医ID</t>
-        </is>
-      </c>
+      <c r="A135" s="27" t="inlineStr">
+        <is>
+          <t>▶ medical_histories</t>
+        </is>
+      </c>
+      <c r="B135" s="29" t="n"/>
+      <c r="C135" s="29" t="n"/>
+      <c r="D135" s="29" t="n"/>
+      <c r="E135" s="29" t="n"/>
+      <c r="F135" s="29" t="n"/>
+      <c r="G135" s="30" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="26" t="inlineStr">
@@ -5845,12 +5840,12 @@
       </c>
       <c r="B136" s="26" t="inlineStr">
         <is>
-          <t>visit_date</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C136" s="26" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D136" s="26" t="inlineStr">
@@ -5858,11 +5853,19 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E136" s="26" t="inlineStr"/>
-      <c r="F136" s="26" t="inlineStr"/>
+      <c r="E136" s="26" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F136" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G136" s="26" t="inlineStr">
         <is>
-          <t>来院日</t>
+          <t>診療記録ID</t>
         </is>
       </c>
     </row>
@@ -5874,12 +5877,12 @@
       </c>
       <c r="B137" s="26" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>appointment_id</t>
         </is>
       </c>
       <c r="C137" s="26" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D137" s="26" t="inlineStr">
@@ -5892,10 +5895,14 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="F137" s="26" t="inlineStr"/>
+      <c r="F137" s="26" t="inlineStr">
+        <is>
+          <t>FK → appointments.id UNIQUE</t>
+        </is>
+      </c>
       <c r="G137" s="26" t="inlineStr">
         <is>
-          <t>診断</t>
+          <t>予約ID</t>
         </is>
       </c>
     </row>
@@ -5907,28 +5914,28 @@
       </c>
       <c r="B138" s="26" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>pet_id</t>
         </is>
       </c>
       <c r="C138" s="26" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D138" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E138" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F138" s="26" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E138" s="26" t="inlineStr"/>
+      <c r="F138" s="26" t="inlineStr">
+        <is>
+          <t>FK → pets.id</t>
+        </is>
+      </c>
       <c r="G138" s="26" t="inlineStr">
         <is>
-          <t>処置</t>
+          <t>ペットID</t>
         </is>
       </c>
     </row>
@@ -5940,28 +5947,28 @@
       </c>
       <c r="B139" s="26" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C139" s="26" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D139" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E139" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F139" s="26" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E139" s="26" t="inlineStr"/>
+      <c r="F139" s="26" t="inlineStr">
+        <is>
+          <t>FK → users.id</t>
+        </is>
+      </c>
       <c r="G139" s="26" t="inlineStr">
         <is>
-          <t>処方</t>
+          <t>担当獣医ID</t>
         </is>
       </c>
     </row>
@@ -5973,28 +5980,24 @@
       </c>
       <c r="B140" s="26" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>visit_date</t>
         </is>
       </c>
       <c r="C140" s="26" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D140" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E140" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E140" s="26" t="inlineStr"/>
       <c r="F140" s="26" t="inlineStr"/>
       <c r="G140" s="26" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>来院日</t>
         </is>
       </c>
     </row>
@@ -6006,12 +6009,12 @@
       </c>
       <c r="B141" s="26" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C141" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D141" s="26" t="inlineStr">
@@ -6027,7 +6030,7 @@
       <c r="F141" s="26" t="inlineStr"/>
       <c r="G141" s="26" t="inlineStr">
         <is>
-          <t>論理削除日時</t>
+          <t>診断</t>
         </is>
       </c>
     </row>
@@ -6039,28 +6042,28 @@
       </c>
       <c r="B142" s="26" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>treatment</t>
         </is>
       </c>
       <c r="C142" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D142" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E142" s="26" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="F142" s="26" t="inlineStr"/>
       <c r="G142" s="26" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>処置</t>
         </is>
       </c>
     </row>
@@ -6072,95 +6075,111 @@
       </c>
       <c r="B143" s="26" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="C143" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D143" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E143" s="26" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="F143" s="26" t="inlineStr"/>
       <c r="G143" s="26" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>処方</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="27" t="inlineStr">
-        <is>
-          <t>▶ medical_attachments</t>
-        </is>
-      </c>
-      <c r="B144" s="29" t="n"/>
-      <c r="C144" s="29" t="n"/>
-      <c r="D144" s="29" t="n"/>
-      <c r="E144" s="29" t="n"/>
-      <c r="F144" s="29" t="n"/>
-      <c r="G144" s="30" t="n"/>
+      <c r="A144" s="26" t="inlineStr">
+        <is>
+          <t>medical_histories</t>
+        </is>
+      </c>
+      <c r="B144" s="26" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="C144" s="26" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D144" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E144" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F144" s="26" t="inlineStr"/>
+      <c r="G144" s="26" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="26" t="inlineStr">
         <is>
-          <t>medical_attachments</t>
+          <t>medical_histories</t>
         </is>
       </c>
       <c r="B145" s="26" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C145" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D145" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E145" s="26" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="F145" s="26" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F145" s="26" t="inlineStr"/>
       <c r="G145" s="26" t="inlineStr">
         <is>
-          <t>添付ID</t>
+          <t>論理削除日時</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="26" t="inlineStr">
         <is>
-          <t>medical_attachments</t>
+          <t>medical_histories</t>
         </is>
       </c>
       <c r="B146" s="26" t="inlineStr">
         <is>
-          <t>medical_history_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C146" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D146" s="26" t="inlineStr">
@@ -6168,32 +6187,32 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E146" s="26" t="inlineStr"/>
-      <c r="F146" s="26" t="inlineStr">
-        <is>
-          <t>FK → medical_histories.id</t>
-        </is>
-      </c>
+      <c r="E146" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="F146" s="26" t="inlineStr"/>
       <c r="G146" s="26" t="inlineStr">
         <is>
-          <t>診療記録ID</t>
+          <t>作成日時</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="26" t="inlineStr">
         <is>
-          <t>medical_attachments</t>
+          <t>medical_histories</t>
         </is>
       </c>
       <c r="B147" s="26" t="inlineStr">
         <is>
-          <t>file_path</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C147" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D147" s="26" t="inlineStr">
@@ -6201,46 +6220,30 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E147" s="26" t="inlineStr"/>
+      <c r="E147" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="F147" s="26" t="inlineStr"/>
       <c r="G147" s="26" t="inlineStr">
         <is>
-          <t>ファイルパス</t>
+          <t>更新日時</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="26" t="inlineStr">
-        <is>
-          <t>medical_attachments</t>
-        </is>
-      </c>
-      <c r="B148" s="26" t="inlineStr">
-        <is>
-          <t>file_type</t>
-        </is>
-      </c>
-      <c r="C148" s="26" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D148" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E148" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F148" s="26" t="inlineStr"/>
-      <c r="G148" s="26" t="inlineStr">
-        <is>
-          <t>ファイル種別</t>
-        </is>
-      </c>
+      <c r="A148" s="27" t="inlineStr">
+        <is>
+          <t>▶ medical_attachments</t>
+        </is>
+      </c>
+      <c r="B148" s="29" t="n"/>
+      <c r="C148" s="29" t="n"/>
+      <c r="D148" s="29" t="n"/>
+      <c r="E148" s="29" t="n"/>
+      <c r="F148" s="29" t="n"/>
+      <c r="G148" s="30" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="26" t="inlineStr">
@@ -6250,12 +6253,12 @@
       </c>
       <c r="B149" s="26" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C149" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D149" s="26" t="inlineStr">
@@ -6265,43 +6268,67 @@
       </c>
       <c r="E149" s="26" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="F149" s="26" t="inlineStr"/>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F149" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G149" s="26" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>添付ID</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="27" t="inlineStr">
-        <is>
-          <t>▶ consult_chat_messages</t>
-        </is>
-      </c>
-      <c r="B150" s="29" t="n"/>
-      <c r="C150" s="29" t="n"/>
-      <c r="D150" s="29" t="n"/>
-      <c r="E150" s="29" t="n"/>
-      <c r="F150" s="29" t="n"/>
-      <c r="G150" s="30" t="n"/>
+      <c r="A150" s="26" t="inlineStr">
+        <is>
+          <t>medical_attachments</t>
+        </is>
+      </c>
+      <c r="B150" s="26" t="inlineStr">
+        <is>
+          <t>medical_history_id</t>
+        </is>
+      </c>
+      <c r="C150" s="26" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D150" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E150" s="26" t="inlineStr"/>
+      <c r="F150" s="26" t="inlineStr">
+        <is>
+          <t>FK → medical_histories.id</t>
+        </is>
+      </c>
+      <c r="G150" s="26" t="inlineStr">
+        <is>
+          <t>診療記録ID</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="26" t="inlineStr">
         <is>
-          <t>consult_chat_messages</t>
+          <t>medical_attachments</t>
         </is>
       </c>
       <c r="B151" s="26" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>file_path</t>
         </is>
       </c>
       <c r="C151" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="D151" s="26" t="inlineStr">
@@ -6309,69 +6336,61 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E151" s="26" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="F151" s="26" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="E151" s="26" t="inlineStr"/>
+      <c r="F151" s="26" t="inlineStr"/>
       <c r="G151" s="26" t="inlineStr">
         <is>
-          <t>メッセージID</t>
+          <t>ファイルパス</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="26" t="inlineStr">
         <is>
-          <t>consult_chat_messages</t>
+          <t>medical_attachments</t>
         </is>
       </c>
       <c r="B152" s="26" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>file_type</t>
         </is>
       </c>
       <c r="C152" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="D152" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E152" s="26" t="inlineStr"/>
-      <c r="F152" s="26" t="inlineStr">
-        <is>
-          <t>FK → users.id</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E152" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F152" s="26" t="inlineStr"/>
       <c r="G152" s="26" t="inlineStr">
         <is>
-          <t>ユーザーID</t>
+          <t>ファイル種別</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="26" t="inlineStr">
         <is>
-          <t>consult_chat_messages</t>
+          <t>medical_attachments</t>
         </is>
       </c>
       <c r="B153" s="26" t="inlineStr">
         <is>
-          <t>channel</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C153" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D153" s="26" t="inlineStr">
@@ -6379,42 +6398,30 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E153" s="26" t="inlineStr"/>
+      <c r="E153" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="F153" s="26" t="inlineStr"/>
       <c r="G153" s="26" t="inlineStr">
         <is>
-          <t>チャンネル種別</t>
+          <t>作成日時</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="26" t="inlineStr">
-        <is>
-          <t>consult_chat_messages</t>
-        </is>
-      </c>
-      <c r="B154" s="26" t="inlineStr">
-        <is>
-          <t>sender_type</t>
-        </is>
-      </c>
-      <c r="C154" s="26" t="inlineStr">
-        <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="D154" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E154" s="26" t="inlineStr"/>
-      <c r="F154" s="26" t="inlineStr"/>
-      <c r="G154" s="26" t="inlineStr">
-        <is>
-          <t>送信者種別</t>
-        </is>
-      </c>
+      <c r="A154" s="27" t="inlineStr">
+        <is>
+          <t>▶ consult_chat_messages</t>
+        </is>
+      </c>
+      <c r="B154" s="29" t="n"/>
+      <c r="C154" s="29" t="n"/>
+      <c r="D154" s="29" t="n"/>
+      <c r="E154" s="29" t="n"/>
+      <c r="F154" s="29" t="n"/>
+      <c r="G154" s="30" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="26" t="inlineStr">
@@ -6424,12 +6431,12 @@
       </c>
       <c r="B155" s="26" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C155" s="26" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D155" s="26" t="inlineStr">
@@ -6437,11 +6444,19 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E155" s="26" t="inlineStr"/>
-      <c r="F155" s="26" t="inlineStr"/>
+      <c r="E155" s="26" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F155" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G155" s="26" t="inlineStr">
         <is>
-          <t>メッセージ本文</t>
+          <t>メッセージID</t>
         </is>
       </c>
     </row>
@@ -6453,12 +6468,12 @@
       </c>
       <c r="B156" s="26" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C156" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D156" s="26" t="inlineStr">
@@ -6466,45 +6481,61 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E156" s="26" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="F156" s="26" t="inlineStr"/>
+      <c r="E156" s="26" t="inlineStr"/>
+      <c r="F156" s="26" t="inlineStr">
+        <is>
+          <t>FK → users.id</t>
+        </is>
+      </c>
       <c r="G156" s="26" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>ユーザーID</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="27" t="inlineStr">
-        <is>
-          <t>▶ notifications</t>
-        </is>
-      </c>
-      <c r="B157" s="29" t="n"/>
-      <c r="C157" s="29" t="n"/>
-      <c r="D157" s="29" t="n"/>
-      <c r="E157" s="29" t="n"/>
-      <c r="F157" s="29" t="n"/>
-      <c r="G157" s="30" t="n"/>
+      <c r="A157" s="26" t="inlineStr">
+        <is>
+          <t>consult_chat_messages</t>
+        </is>
+      </c>
+      <c r="B157" s="26" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="C157" s="26" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="D157" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E157" s="26" t="inlineStr"/>
+      <c r="F157" s="26" t="inlineStr"/>
+      <c r="G157" s="26" t="inlineStr">
+        <is>
+          <t>チャンネル種別</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="26" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>consult_chat_messages</t>
         </is>
       </c>
       <c r="B158" s="26" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>sender_type</t>
         </is>
       </c>
       <c r="C158" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D158" s="26" t="inlineStr">
@@ -6512,36 +6543,28 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E158" s="26" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="F158" s="26" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="E158" s="26" t="inlineStr"/>
+      <c r="F158" s="26" t="inlineStr"/>
       <c r="G158" s="26" t="inlineStr">
         <is>
-          <t>通知ID</t>
+          <t>送信者種別</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="26" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>consult_chat_messages</t>
         </is>
       </c>
       <c r="B159" s="26" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>content</t>
         </is>
       </c>
       <c r="C159" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D159" s="26" t="inlineStr">
@@ -6553,24 +6576,24 @@
       <c r="F159" s="26" t="inlineStr"/>
       <c r="G159" s="26" t="inlineStr">
         <is>
-          <t>通知種別</t>
+          <t>メッセージ本文</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="26" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>consult_chat_messages</t>
         </is>
       </c>
       <c r="B160" s="26" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C160" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D160" s="26" t="inlineStr">
@@ -6578,46 +6601,30 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E160" s="26" t="inlineStr"/>
+      <c r="E160" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="F160" s="26" t="inlineStr"/>
       <c r="G160" s="26" t="inlineStr">
         <is>
-          <t>タイトル</t>
+          <t>作成日時</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="26" t="inlineStr">
-        <is>
-          <t>notifications</t>
-        </is>
-      </c>
-      <c r="B161" s="26" t="inlineStr">
-        <is>
-          <t>body</t>
-        </is>
-      </c>
-      <c r="C161" s="26" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D161" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E161" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F161" s="26" t="inlineStr"/>
-      <c r="G161" s="26" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
+      <c r="A161" s="27" t="inlineStr">
+        <is>
+          <t>▶ notifications</t>
+        </is>
+      </c>
+      <c r="B161" s="29" t="n"/>
+      <c r="C161" s="29" t="n"/>
+      <c r="D161" s="29" t="n"/>
+      <c r="E161" s="29" t="n"/>
+      <c r="F161" s="29" t="n"/>
+      <c r="G161" s="30" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="26" t="inlineStr">
@@ -6627,12 +6634,12 @@
       </c>
       <c r="B162" s="26" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C162" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D162" s="26" t="inlineStr">
@@ -6642,43 +6649,63 @@
       </c>
       <c r="E162" s="26" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="F162" s="26" t="inlineStr"/>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F162" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G162" s="26" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>通知ID</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="27" t="inlineStr">
-        <is>
-          <t>▶ notification_recipients</t>
-        </is>
-      </c>
-      <c r="B163" s="29" t="n"/>
-      <c r="C163" s="29" t="n"/>
-      <c r="D163" s="29" t="n"/>
-      <c r="E163" s="29" t="n"/>
-      <c r="F163" s="29" t="n"/>
-      <c r="G163" s="30" t="n"/>
+      <c r="A163" s="26" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+      <c r="B163" s="26" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C163" s="26" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="D163" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E163" s="26" t="inlineStr"/>
+      <c r="F163" s="26" t="inlineStr"/>
+      <c r="G163" s="26" t="inlineStr">
+        <is>
+          <t>通知種別</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="26" t="inlineStr">
         <is>
-          <t>notification_recipients</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="B164" s="26" t="inlineStr">
         <is>
-          <t>notification_id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C164" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="D164" s="26" t="inlineStr">
@@ -6687,64 +6714,60 @@
         </is>
       </c>
       <c r="E164" s="26" t="inlineStr"/>
-      <c r="F164" s="26" t="inlineStr">
-        <is>
-          <t>PK, FK → notifications.id</t>
-        </is>
-      </c>
+      <c r="F164" s="26" t="inlineStr"/>
       <c r="G164" s="26" t="inlineStr">
         <is>
-          <t>通知ID</t>
+          <t>タイトル</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="26" t="inlineStr">
         <is>
-          <t>notification_recipients</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="B165" s="26" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>body</t>
         </is>
       </c>
       <c r="C165" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D165" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E165" s="26" t="inlineStr"/>
-      <c r="F165" s="26" t="inlineStr">
-        <is>
-          <t>PK, FK → users.id</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E165" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F165" s="26" t="inlineStr"/>
       <c r="G165" s="26" t="inlineStr">
         <is>
-          <t>ユーザーID</t>
+          <t>本文</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="26" t="inlineStr">
         <is>
-          <t>notification_recipients</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="B166" s="26" t="inlineStr">
         <is>
-          <t>is_read</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C166" s="26" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D166" s="26" t="inlineStr">
@@ -6754,71 +6777,71 @@
       </c>
       <c r="E166" s="26" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
       <c r="F166" s="26" t="inlineStr"/>
       <c r="G166" s="26" t="inlineStr">
         <is>
-          <t>既読フラグ</t>
+          <t>作成日時</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="26" t="inlineStr">
+      <c r="A167" s="27" t="inlineStr">
+        <is>
+          <t>▶ notification_recipients</t>
+        </is>
+      </c>
+      <c r="B167" s="29" t="n"/>
+      <c r="C167" s="29" t="n"/>
+      <c r="D167" s="29" t="n"/>
+      <c r="E167" s="29" t="n"/>
+      <c r="F167" s="29" t="n"/>
+      <c r="G167" s="30" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="26" t="inlineStr">
         <is>
           <t>notification_recipients</t>
         </is>
       </c>
-      <c r="B167" s="26" t="inlineStr">
-        <is>
-          <t>read_at</t>
-        </is>
-      </c>
-      <c r="C167" s="26" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D167" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E167" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F167" s="26" t="inlineStr"/>
-      <c r="G167" s="26" t="inlineStr">
-        <is>
-          <t>既読日時</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="27" t="inlineStr">
-        <is>
-          <t>▶ email_templates</t>
-        </is>
-      </c>
-      <c r="B168" s="29" t="n"/>
-      <c r="C168" s="29" t="n"/>
-      <c r="D168" s="29" t="n"/>
-      <c r="E168" s="29" t="n"/>
-      <c r="F168" s="29" t="n"/>
-      <c r="G168" s="30" t="n"/>
+      <c r="B168" s="26" t="inlineStr">
+        <is>
+          <t>notification_id</t>
+        </is>
+      </c>
+      <c r="C168" s="26" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D168" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E168" s="26" t="inlineStr"/>
+      <c r="F168" s="26" t="inlineStr">
+        <is>
+          <t>PK, FK → notifications.id</t>
+        </is>
+      </c>
+      <c r="G168" s="26" t="inlineStr">
+        <is>
+          <t>通知ID</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="26" t="inlineStr">
         <is>
-          <t>email_templates</t>
+          <t>notification_recipients</t>
         </is>
       </c>
       <c r="B169" s="26" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C169" s="26" t="inlineStr">
@@ -6831,36 +6854,32 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E169" s="26" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
+      <c r="E169" s="26" t="inlineStr"/>
       <c r="F169" s="26" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>PK, FK → users.id</t>
         </is>
       </c>
       <c r="G169" s="26" t="inlineStr">
         <is>
-          <t>テンプレートID</t>
+          <t>ユーザーID</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="26" t="inlineStr">
         <is>
-          <t>email_templates</t>
+          <t>notification_recipients</t>
         </is>
       </c>
       <c r="B170" s="26" t="inlineStr">
         <is>
-          <t>template_code</t>
+          <t>is_read</t>
         </is>
       </c>
       <c r="C170" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="D170" s="26" t="inlineStr">
@@ -6868,75 +6887,63 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E170" s="26" t="inlineStr"/>
-      <c r="F170" s="26" t="inlineStr">
-        <is>
-          <t>UNIQUE</t>
-        </is>
-      </c>
+      <c r="E170" s="26" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F170" s="26" t="inlineStr"/>
       <c r="G170" s="26" t="inlineStr">
         <is>
-          <t>テンプレートコード</t>
+          <t>既読フラグ</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="26" t="inlineStr">
         <is>
-          <t>email_templates</t>
+          <t>notification_recipients</t>
         </is>
       </c>
       <c r="B171" s="26" t="inlineStr">
         <is>
-          <t>subject</t>
+          <t>read_at</t>
         </is>
       </c>
       <c r="C171" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(255)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D171" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E171" s="26" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E171" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="F171" s="26" t="inlineStr"/>
       <c r="G171" s="26" t="inlineStr">
         <is>
-          <t>件名</t>
+          <t>既読日時</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="26" t="inlineStr">
-        <is>
-          <t>email_templates</t>
-        </is>
-      </c>
-      <c r="B172" s="26" t="inlineStr">
-        <is>
-          <t>body</t>
-        </is>
-      </c>
-      <c r="C172" s="26" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D172" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E172" s="26" t="inlineStr"/>
-      <c r="F172" s="26" t="inlineStr"/>
-      <c r="G172" s="26" t="inlineStr">
-        <is>
-          <t>本文テンプレート</t>
-        </is>
-      </c>
+      <c r="A172" s="27" t="inlineStr">
+        <is>
+          <t>▶ email_templates</t>
+        </is>
+      </c>
+      <c r="B172" s="29" t="n"/>
+      <c r="C172" s="29" t="n"/>
+      <c r="D172" s="29" t="n"/>
+      <c r="E172" s="29" t="n"/>
+      <c r="F172" s="29" t="n"/>
+      <c r="G172" s="30" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="26" t="inlineStr">
@@ -6946,12 +6953,12 @@
       </c>
       <c r="B173" s="26" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C173" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D173" s="26" t="inlineStr">
@@ -6961,13 +6968,17 @@
       </c>
       <c r="E173" s="26" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="F173" s="26" t="inlineStr"/>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F173" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G173" s="26" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>テンプレートID</t>
         </is>
       </c>
     </row>
@@ -6979,12 +6990,12 @@
       </c>
       <c r="B174" s="26" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>template_code</t>
         </is>
       </c>
       <c r="C174" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="D174" s="26" t="inlineStr">
@@ -6992,45 +7003,61 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E174" s="26" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="F174" s="26" t="inlineStr"/>
+      <c r="E174" s="26" t="inlineStr"/>
+      <c r="F174" s="26" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
       <c r="G174" s="26" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>テンプレートコード</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="27" t="inlineStr">
-        <is>
-          <t>▶ email_messages</t>
-        </is>
-      </c>
-      <c r="B175" s="29" t="n"/>
-      <c r="C175" s="29" t="n"/>
-      <c r="D175" s="29" t="n"/>
-      <c r="E175" s="29" t="n"/>
-      <c r="F175" s="29" t="n"/>
-      <c r="G175" s="30" t="n"/>
+      <c r="A175" s="26" t="inlineStr">
+        <is>
+          <t>email_templates</t>
+        </is>
+      </c>
+      <c r="B175" s="26" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="C175" s="26" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="D175" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E175" s="26" t="inlineStr"/>
+      <c r="F175" s="26" t="inlineStr"/>
+      <c r="G175" s="26" t="inlineStr">
+        <is>
+          <t>件名</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="26" t="inlineStr">
         <is>
-          <t>email_messages</t>
+          <t>email_templates</t>
         </is>
       </c>
       <c r="B176" s="26" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>body</t>
         </is>
       </c>
       <c r="C176" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D176" s="26" t="inlineStr">
@@ -7038,73 +7065,61 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E176" s="26" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="F176" s="26" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="E176" s="26" t="inlineStr"/>
+      <c r="F176" s="26" t="inlineStr"/>
       <c r="G176" s="26" t="inlineStr">
         <is>
-          <t>メールID</t>
+          <t>本文テンプレート</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="26" t="inlineStr">
         <is>
-          <t>email_messages</t>
+          <t>email_templates</t>
         </is>
       </c>
       <c r="B177" s="26" t="inlineStr">
         <is>
-          <t>template_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C177" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D177" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E177" s="26" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F177" s="26" t="inlineStr">
-        <is>
-          <t>FK → email_templates.id</t>
-        </is>
-      </c>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="F177" s="26" t="inlineStr"/>
       <c r="G177" s="26" t="inlineStr">
         <is>
-          <t>テンプレートID</t>
+          <t>作成日時</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="26" t="inlineStr">
         <is>
-          <t>email_messages</t>
+          <t>email_templates</t>
         </is>
       </c>
       <c r="B178" s="26" t="inlineStr">
         <is>
-          <t>to_address</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C178" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(255)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D178" s="26" t="inlineStr">
@@ -7112,42 +7127,30 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E178" s="26" t="inlineStr"/>
+      <c r="E178" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="F178" s="26" t="inlineStr"/>
       <c r="G178" s="26" t="inlineStr">
         <is>
-          <t>宛先</t>
+          <t>更新日時</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="26" t="inlineStr">
-        <is>
-          <t>email_messages</t>
-        </is>
-      </c>
-      <c r="B179" s="26" t="inlineStr">
-        <is>
-          <t>subject</t>
-        </is>
-      </c>
-      <c r="C179" s="26" t="inlineStr">
-        <is>
-          <t>VARCHAR(255)</t>
-        </is>
-      </c>
-      <c r="D179" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E179" s="26" t="inlineStr"/>
-      <c r="F179" s="26" t="inlineStr"/>
-      <c r="G179" s="26" t="inlineStr">
-        <is>
-          <t>件名</t>
-        </is>
-      </c>
+      <c r="A179" s="27" t="inlineStr">
+        <is>
+          <t>▶ email_messages</t>
+        </is>
+      </c>
+      <c r="B179" s="29" t="n"/>
+      <c r="C179" s="29" t="n"/>
+      <c r="D179" s="29" t="n"/>
+      <c r="E179" s="29" t="n"/>
+      <c r="F179" s="29" t="n"/>
+      <c r="G179" s="30" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="26" t="inlineStr">
@@ -7157,12 +7160,12 @@
       </c>
       <c r="B180" s="26" t="inlineStr">
         <is>
-          <t>body</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C180" s="26" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D180" s="26" t="inlineStr">
@@ -7170,11 +7173,19 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E180" s="26" t="inlineStr"/>
-      <c r="F180" s="26" t="inlineStr"/>
+      <c r="E180" s="26" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F180" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G180" s="26" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>メールID</t>
         </is>
       </c>
     </row>
@@ -7186,28 +7197,32 @@
       </c>
       <c r="B181" s="26" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>template_id</t>
         </is>
       </c>
       <c r="C181" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D181" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E181" s="26" t="inlineStr">
         <is>
-          <t>'PENDING'</t>
-        </is>
-      </c>
-      <c r="F181" s="26" t="inlineStr"/>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F181" s="26" t="inlineStr">
+        <is>
+          <t>FK → email_templates.id</t>
+        </is>
+      </c>
       <c r="G181" s="26" t="inlineStr">
         <is>
-          <t>送信状態</t>
+          <t>テンプレートID</t>
         </is>
       </c>
     </row>
@@ -7219,28 +7234,24 @@
       </c>
       <c r="B182" s="26" t="inlineStr">
         <is>
-          <t>sent_at</t>
+          <t>to_address</t>
         </is>
       </c>
       <c r="C182" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(255)</t>
         </is>
       </c>
       <c r="D182" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E182" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E182" s="26" t="inlineStr"/>
       <c r="F182" s="26" t="inlineStr"/>
       <c r="G182" s="26" t="inlineStr">
         <is>
-          <t>送信日時</t>
+          <t>宛先</t>
         </is>
       </c>
     </row>
@@ -7252,12 +7263,12 @@
       </c>
       <c r="B183" s="26" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>subject</t>
         </is>
       </c>
       <c r="C183" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(255)</t>
         </is>
       </c>
       <c r="D183" s="26" t="inlineStr">
@@ -7265,45 +7276,57 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E183" s="26" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="E183" s="26" t="inlineStr"/>
       <c r="F183" s="26" t="inlineStr"/>
       <c r="G183" s="26" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>件名</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="27" t="inlineStr">
-        <is>
-          <t>▶ pet_calendar_marks</t>
-        </is>
-      </c>
-      <c r="B184" s="29" t="n"/>
-      <c r="C184" s="29" t="n"/>
-      <c r="D184" s="29" t="n"/>
-      <c r="E184" s="29" t="n"/>
-      <c r="F184" s="29" t="n"/>
-      <c r="G184" s="30" t="n"/>
+      <c r="A184" s="26" t="inlineStr">
+        <is>
+          <t>email_messages</t>
+        </is>
+      </c>
+      <c r="B184" s="26" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="C184" s="26" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D184" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E184" s="26" t="inlineStr"/>
+      <c r="F184" s="26" t="inlineStr"/>
+      <c r="G184" s="26" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="26" t="inlineStr">
         <is>
-          <t>pet_calendar_marks</t>
+          <t>email_messages</t>
         </is>
       </c>
       <c r="B185" s="26" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C185" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D185" s="26" t="inlineStr">
@@ -7313,67 +7336,63 @@
       </c>
       <c r="E185" s="26" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="F185" s="26" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>'PENDING'</t>
+        </is>
+      </c>
+      <c r="F185" s="26" t="inlineStr"/>
       <c r="G185" s="26" t="inlineStr">
         <is>
-          <t>マークID</t>
+          <t>送信状態</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="26" t="inlineStr">
         <is>
-          <t>pet_calendar_marks</t>
+          <t>email_messages</t>
         </is>
       </c>
       <c r="B186" s="26" t="inlineStr">
         <is>
-          <t>pet_id</t>
+          <t>sent_at</t>
         </is>
       </c>
       <c r="C186" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D186" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E186" s="26" t="inlineStr"/>
-      <c r="F186" s="26" t="inlineStr">
-        <is>
-          <t>FK → pets.id</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E186" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F186" s="26" t="inlineStr"/>
       <c r="G186" s="26" t="inlineStr">
         <is>
-          <t>ペットID</t>
+          <t>送信日時</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="26" t="inlineStr">
         <is>
-          <t>pet_calendar_marks</t>
+          <t>email_messages</t>
         </is>
       </c>
       <c r="B187" s="26" t="inlineStr">
         <is>
-          <t>mark_date</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C187" s="26" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D187" s="26" t="inlineStr">
@@ -7381,46 +7400,30 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E187" s="26" t="inlineStr"/>
+      <c r="E187" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="F187" s="26" t="inlineStr"/>
       <c r="G187" s="26" t="inlineStr">
         <is>
-          <t>マーク日</t>
+          <t>作成日時</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="26" t="inlineStr">
-        <is>
-          <t>pet_calendar_marks</t>
-        </is>
-      </c>
-      <c r="B188" s="26" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="C188" s="26" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="D188" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E188" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F188" s="26" t="inlineStr"/>
-      <c r="G188" s="26" t="inlineStr">
-        <is>
-          <t>ラベル</t>
-        </is>
-      </c>
+      <c r="A188" s="27" t="inlineStr">
+        <is>
+          <t>▶ pet_calendar_marks</t>
+        </is>
+      </c>
+      <c r="B188" s="29" t="n"/>
+      <c r="C188" s="29" t="n"/>
+      <c r="D188" s="29" t="n"/>
+      <c r="E188" s="29" t="n"/>
+      <c r="F188" s="29" t="n"/>
+      <c r="G188" s="30" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="26" t="inlineStr">
@@ -7430,28 +7433,32 @@
       </c>
       <c r="B189" s="26" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C189" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D189" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E189" s="26" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F189" s="26" t="inlineStr"/>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F189" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G189" s="26" t="inlineStr">
         <is>
-          <t>色</t>
+          <t>マークID</t>
         </is>
       </c>
     </row>
@@ -7463,28 +7470,28 @@
       </c>
       <c r="B190" s="26" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>pet_id</t>
         </is>
       </c>
       <c r="C190" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D190" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E190" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F190" s="26" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E190" s="26" t="inlineStr"/>
+      <c r="F190" s="26" t="inlineStr">
+        <is>
+          <t>FK → pets.id</t>
+        </is>
+      </c>
       <c r="G190" s="26" t="inlineStr">
         <is>
-          <t>論理削除日時</t>
+          <t>ペットID</t>
         </is>
       </c>
     </row>
@@ -7496,12 +7503,12 @@
       </c>
       <c r="B191" s="26" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>mark_date</t>
         </is>
       </c>
       <c r="C191" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D191" s="26" t="inlineStr">
@@ -7509,15 +7516,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E191" s="26" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="E191" s="26" t="inlineStr"/>
       <c r="F191" s="26" t="inlineStr"/>
       <c r="G191" s="26" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>マーク日</t>
         </is>
       </c>
     </row>
@@ -7529,95 +7532,111 @@
       </c>
       <c r="B192" s="26" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>label</t>
         </is>
       </c>
       <c r="C192" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D192" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E192" s="26" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="F192" s="26" t="inlineStr"/>
       <c r="G192" s="26" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>ラベル</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="27" t="inlineStr">
-        <is>
-          <t>▶ dismissed_reminders</t>
-        </is>
-      </c>
-      <c r="B193" s="29" t="n"/>
-      <c r="C193" s="29" t="n"/>
-      <c r="D193" s="29" t="n"/>
-      <c r="E193" s="29" t="n"/>
-      <c r="F193" s="29" t="n"/>
-      <c r="G193" s="30" t="n"/>
+      <c r="A193" s="26" t="inlineStr">
+        <is>
+          <t>pet_calendar_marks</t>
+        </is>
+      </c>
+      <c r="B193" s="26" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="C193" s="26" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="D193" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E193" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F193" s="26" t="inlineStr"/>
+      <c r="G193" s="26" t="inlineStr">
+        <is>
+          <t>色</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="26" t="inlineStr">
         <is>
-          <t>dismissed_reminders</t>
+          <t>pet_calendar_marks</t>
         </is>
       </c>
       <c r="B194" s="26" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C194" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D194" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E194" s="26" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="F194" s="26" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F194" s="26" t="inlineStr"/>
       <c r="G194" s="26" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>論理削除日時</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="26" t="inlineStr">
         <is>
-          <t>dismissed_reminders</t>
+          <t>pet_calendar_marks</t>
         </is>
       </c>
       <c r="B195" s="26" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C195" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D195" s="26" t="inlineStr">
@@ -7625,106 +7644,110 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E195" s="26" t="inlineStr"/>
-      <c r="F195" s="26" t="inlineStr">
-        <is>
-          <t>FK → users.id</t>
-        </is>
-      </c>
+      <c r="E195" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="F195" s="26" t="inlineStr"/>
       <c r="G195" s="26" t="inlineStr">
         <is>
-          <t>ユーザーID</t>
+          <t>作成日時</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="26" t="inlineStr">
         <is>
+          <t>pet_calendar_marks</t>
+        </is>
+      </c>
+      <c r="B196" s="26" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C196" s="26" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D196" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E196" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="F196" s="26" t="inlineStr"/>
+      <c r="G196" s="26" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="27" t="inlineStr">
+        <is>
+          <t>▶ dismissed_reminders</t>
+        </is>
+      </c>
+      <c r="B197" s="29" t="n"/>
+      <c r="C197" s="29" t="n"/>
+      <c r="D197" s="29" t="n"/>
+      <c r="E197" s="29" t="n"/>
+      <c r="F197" s="29" t="n"/>
+      <c r="G197" s="30" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="26" t="inlineStr">
+        <is>
           <t>dismissed_reminders</t>
         </is>
       </c>
-      <c r="B196" s="26" t="inlineStr">
-        <is>
-          <t>reminder_key</t>
-        </is>
-      </c>
-      <c r="C196" s="26" t="inlineStr">
-        <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
-      <c r="D196" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E196" s="26" t="inlineStr"/>
-      <c r="F196" s="26" t="inlineStr">
-        <is>
-          <t>UNIQUE(user_id,reminder_key)</t>
-        </is>
-      </c>
-      <c r="G196" s="26" t="inlineStr">
-        <is>
-          <t>リマインダーキー</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="26" t="inlineStr">
-        <is>
-          <t>dismissed_reminders</t>
-        </is>
-      </c>
-      <c r="B197" s="26" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C197" s="26" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D197" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E197" s="26" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="F197" s="26" t="inlineStr"/>
-      <c r="G197" s="26" t="inlineStr">
-        <is>
-          <t>作成日時</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="27" t="inlineStr">
-        <is>
-          <t>▶ announcements</t>
-        </is>
-      </c>
-      <c r="B198" s="29" t="n"/>
-      <c r="C198" s="29" t="n"/>
-      <c r="D198" s="29" t="n"/>
-      <c r="E198" s="29" t="n"/>
-      <c r="F198" s="29" t="n"/>
-      <c r="G198" s="30" t="n"/>
+      <c r="B198" s="26" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C198" s="26" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D198" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E198" s="26" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F198" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G198" s="26" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="26" t="inlineStr">
         <is>
-          <t>announcements</t>
+          <t>dismissed_reminders</t>
         </is>
       </c>
       <c r="B199" s="26" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C199" s="26" t="inlineStr">
@@ -7737,31 +7760,27 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E199" s="26" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
+      <c r="E199" s="26" t="inlineStr"/>
       <c r="F199" s="26" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>FK → users.id</t>
         </is>
       </c>
       <c r="G199" s="26" t="inlineStr">
         <is>
-          <t>お知らせID</t>
+          <t>ユーザーID</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="26" t="inlineStr">
         <is>
-          <t>announcements</t>
+          <t>dismissed_reminders</t>
         </is>
       </c>
       <c r="B200" s="26" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>reminder_key</t>
         </is>
       </c>
       <c r="C200" s="26" t="inlineStr">
@@ -7775,27 +7794,31 @@
         </is>
       </c>
       <c r="E200" s="26" t="inlineStr"/>
-      <c r="F200" s="26" t="inlineStr"/>
+      <c r="F200" s="26" t="inlineStr">
+        <is>
+          <t>UNIQUE(user_id,reminder_key)</t>
+        </is>
+      </c>
       <c r="G200" s="26" t="inlineStr">
         <is>
-          <t>タイトル</t>
+          <t>リマインダーキー</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="26" t="inlineStr">
         <is>
-          <t>announcements</t>
+          <t>dismissed_reminders</t>
         </is>
       </c>
       <c r="B201" s="26" t="inlineStr">
         <is>
-          <t>body</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C201" s="26" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D201" s="26" t="inlineStr">
@@ -7803,46 +7826,30 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E201" s="26" t="inlineStr"/>
+      <c r="E201" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="F201" s="26" t="inlineStr"/>
       <c r="G201" s="26" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>作成日時</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="26" t="inlineStr">
-        <is>
-          <t>announcements</t>
-        </is>
-      </c>
-      <c r="B202" s="26" t="inlineStr">
-        <is>
-          <t>published_at</t>
-        </is>
-      </c>
-      <c r="C202" s="26" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D202" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E202" s="26" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F202" s="26" t="inlineStr"/>
-      <c r="G202" s="26" t="inlineStr">
-        <is>
-          <t>公開日時</t>
-        </is>
-      </c>
+      <c r="A202" s="27" t="inlineStr">
+        <is>
+          <t>▶ announcements</t>
+        </is>
+      </c>
+      <c r="B202" s="29" t="n"/>
+      <c r="C202" s="29" t="n"/>
+      <c r="D202" s="29" t="n"/>
+      <c r="E202" s="29" t="n"/>
+      <c r="F202" s="29" t="n"/>
+      <c r="G202" s="30" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="26" t="inlineStr">
@@ -7852,28 +7859,32 @@
       </c>
       <c r="B203" s="26" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C203" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D203" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E203" s="26" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F203" s="26" t="inlineStr"/>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F203" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G203" s="26" t="inlineStr">
         <is>
-          <t>論理削除日時</t>
+          <t>お知らせID</t>
         </is>
       </c>
     </row>
@@ -7885,12 +7896,12 @@
       </c>
       <c r="B204" s="26" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C204" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="D204" s="26" t="inlineStr">
@@ -7898,15 +7909,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E204" s="26" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="E204" s="26" t="inlineStr"/>
       <c r="F204" s="26" t="inlineStr"/>
       <c r="G204" s="26" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>タイトル</t>
         </is>
       </c>
     </row>
@@ -7918,12 +7925,12 @@
       </c>
       <c r="B205" s="26" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>body</t>
         </is>
       </c>
       <c r="C205" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D205" s="26" t="inlineStr">
@@ -7931,82 +7938,94 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E205" s="26" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="E205" s="26" t="inlineStr"/>
       <c r="F205" s="26" t="inlineStr"/>
       <c r="G205" s="26" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>本文</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="27" t="inlineStr">
-        <is>
-          <t>▶ password_reset_tokens</t>
-        </is>
-      </c>
-      <c r="B206" s="29" t="n"/>
-      <c r="C206" s="29" t="n"/>
-      <c r="D206" s="29" t="n"/>
-      <c r="E206" s="29" t="n"/>
-      <c r="F206" s="29" t="n"/>
-      <c r="G206" s="30" t="n"/>
+      <c r="A206" s="26" t="inlineStr">
+        <is>
+          <t>announcements</t>
+        </is>
+      </c>
+      <c r="B206" s="26" t="inlineStr">
+        <is>
+          <t>published_at</t>
+        </is>
+      </c>
+      <c r="C206" s="26" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D206" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E206" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F206" s="26" t="inlineStr"/>
+      <c r="G206" s="26" t="inlineStr">
+        <is>
+          <t>公開日時</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="26" t="inlineStr">
         <is>
-          <t>password_reset_tokens</t>
+          <t>announcements</t>
         </is>
       </c>
       <c r="B207" s="26" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C207" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D207" s="26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E207" s="26" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="F207" s="26" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F207" s="26" t="inlineStr"/>
       <c r="G207" s="26" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>論理削除日時</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="26" t="inlineStr">
         <is>
-          <t>password_reset_tokens</t>
+          <t>announcements</t>
         </is>
       </c>
       <c r="B208" s="26" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C208" s="26" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D208" s="26" t="inlineStr">
@@ -8014,32 +8033,32 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E208" s="26" t="inlineStr"/>
-      <c r="F208" s="26" t="inlineStr">
-        <is>
-          <t>FK → users.id</t>
-        </is>
-      </c>
+      <c r="E208" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="F208" s="26" t="inlineStr"/>
       <c r="G208" s="26" t="inlineStr">
         <is>
-          <t>ユーザーID</t>
+          <t>作成日時</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="26" t="inlineStr">
         <is>
-          <t>password_reset_tokens</t>
+          <t>announcements</t>
         </is>
       </c>
       <c r="B209" s="26" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C209" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(255)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D209" s="26" t="inlineStr">
@@ -8047,46 +8066,30 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E209" s="26" t="inlineStr"/>
-      <c r="F209" s="26" t="inlineStr">
-        <is>
-          <t>UNIQUE</t>
-        </is>
-      </c>
+      <c r="E209" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="F209" s="26" t="inlineStr"/>
       <c r="G209" s="26" t="inlineStr">
         <is>
-          <t>トークン</t>
+          <t>更新日時</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="26" t="inlineStr">
-        <is>
-          <t>password_reset_tokens</t>
-        </is>
-      </c>
-      <c r="B210" s="26" t="inlineStr">
-        <is>
-          <t>expires_at</t>
-        </is>
-      </c>
-      <c r="C210" s="26" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D210" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E210" s="26" t="inlineStr"/>
-      <c r="F210" s="26" t="inlineStr"/>
-      <c r="G210" s="26" t="inlineStr">
-        <is>
-          <t>有効期限</t>
-        </is>
-      </c>
+      <c r="A210" s="27" t="inlineStr">
+        <is>
+          <t>▶ password_reset_tokens</t>
+        </is>
+      </c>
+      <c r="B210" s="29" t="n"/>
+      <c r="C210" s="29" t="n"/>
+      <c r="D210" s="29" t="n"/>
+      <c r="E210" s="29" t="n"/>
+      <c r="F210" s="29" t="n"/>
+      <c r="G210" s="30" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="26" t="inlineStr">
@@ -8096,28 +8099,32 @@
       </c>
       <c r="B211" s="26" t="inlineStr">
         <is>
-          <t>used_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C211" s="26" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D211" s="26" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E211" s="26" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F211" s="26" t="inlineStr"/>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="F211" s="26" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G211" s="26" t="inlineStr">
         <is>
-          <t>使用日時</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -8129,26 +8136,154 @@
       </c>
       <c r="B212" s="26" t="inlineStr">
         <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C212" s="26" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D212" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E212" s="26" t="inlineStr"/>
+      <c r="F212" s="26" t="inlineStr">
+        <is>
+          <t>FK → users.id</t>
+        </is>
+      </c>
+      <c r="G212" s="26" t="inlineStr">
+        <is>
+          <t>ユーザーID</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="26" t="inlineStr">
+        <is>
+          <t>password_reset_tokens</t>
+        </is>
+      </c>
+      <c r="B213" s="26" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="C213" s="26" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="D213" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E213" s="26" t="inlineStr"/>
+      <c r="F213" s="26" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
+      <c r="G213" s="26" t="inlineStr">
+        <is>
+          <t>トークン</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="26" t="inlineStr">
+        <is>
+          <t>password_reset_tokens</t>
+        </is>
+      </c>
+      <c r="B214" s="26" t="inlineStr">
+        <is>
+          <t>expires_at</t>
+        </is>
+      </c>
+      <c r="C214" s="26" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D214" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E214" s="26" t="inlineStr"/>
+      <c r="F214" s="26" t="inlineStr"/>
+      <c r="G214" s="26" t="inlineStr">
+        <is>
+          <t>有効期限</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="26" t="inlineStr">
+        <is>
+          <t>password_reset_tokens</t>
+        </is>
+      </c>
+      <c r="B215" s="26" t="inlineStr">
+        <is>
+          <t>used_at</t>
+        </is>
+      </c>
+      <c r="C215" s="26" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D215" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E215" s="26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F215" s="26" t="inlineStr"/>
+      <c r="G215" s="26" t="inlineStr">
+        <is>
+          <t>使用日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="26" t="inlineStr">
+        <is>
+          <t>password_reset_tokens</t>
+        </is>
+      </c>
+      <c r="B216" s="26" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C212" s="26" t="inlineStr">
+      <c r="C216" s="26" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="D212" s="26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E212" s="26" t="inlineStr">
+      <c r="D216" s="26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E216" s="26" t="inlineStr">
         <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="F212" s="26" t="inlineStr"/>
-      <c r="G212" s="26" t="inlineStr">
+      <c r="F216" s="26" t="inlineStr"/>
+      <c r="G216" s="26" t="inlineStr">
         <is>
           <t>作成日時</t>
         </is>
@@ -8194,7 +8329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.4921875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="18" min="1" max="1"/>
@@ -8459,12 +8594,12 @@
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>idx_sc_pet</t>
+          <t>idx_symptom_checks_pet_created_at</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>pet_id</t>
+          <t>pet_id, created_at</t>
         </is>
       </c>
       <c r="D13" s="26" t="inlineStr">
@@ -8486,12 +8621,12 @@
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>idx_sc_user</t>
+          <t>idx_symptom_checks_requested_by_user_id</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>requested_by_user_id</t>
         </is>
       </c>
       <c r="D14" s="26" t="inlineStr">
@@ -8501,7 +8636,7 @@
       </c>
       <c r="E14" s="26" t="inlineStr">
         <is>
-          <t>ユーザー別症状チェック履歴</t>
+          <t>依頼者検索・FK結合</t>
         </is>
       </c>
     </row>
@@ -8652,111 +8787,111 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
-        <is>
-          <t>invoices</t>
-        </is>
-      </c>
-      <c r="B21" s="26" t="inlineStr">
-        <is>
-          <t>idx_inv_subscription</t>
-        </is>
-      </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>subscription_id</t>
-        </is>
-      </c>
-      <c r="D21" s="26" t="inlineStr">
-        <is>
-          <t>INDEX</t>
-        </is>
-      </c>
-      <c r="E21" s="26" t="inlineStr">
-        <is>
-          <t>サブスクリプション別請求書検索</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>subscriptions</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>uq_subscriptions_active_user</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>user_id (WHERE deleted_at IS NULL AND status='ACTIVE')</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>UNIQUE (部分)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>アクティブサブスクのユーザー重複防止</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="26" t="inlineStr">
         <is>
+          <t>invoices</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>idx_inv_subscription</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>subscription_id</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>INDEX</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>サブスクリプション別請求書検索</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
           <t>payments</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>idx_pay_invoice</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
         <is>
           <t>invoice_id</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D23" s="26" t="inlineStr">
         <is>
           <t>INDEX</t>
         </is>
       </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>請求書別支払履歴検索</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="28" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>── 予約・診療記録 ──</t>
         </is>
       </c>
-      <c r="B23" s="29" t="n"/>
-      <c r="C23" s="29" t="n"/>
-      <c r="D23" s="29" t="n"/>
-      <c r="E23" s="30" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="26" t="inlineStr">
-        <is>
-          <t>appointment_slots</t>
-        </is>
-      </c>
-      <c r="B24" s="26" t="inlineStr">
-        <is>
-          <t>idx_slots_date</t>
-        </is>
-      </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>slot_date</t>
-        </is>
-      </c>
-      <c r="D24" s="26" t="inlineStr">
-        <is>
-          <t>INDEX</t>
-        </is>
-      </c>
-      <c r="E24" s="26" t="inlineStr">
-        <is>
-          <t>日付別予約枠検索</t>
-        </is>
-      </c>
+      <c r="B24" s="29" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="30" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>appointments</t>
+          <t>appointment_slots</t>
         </is>
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>idx_appt_user</t>
+          <t>idx_slots_date</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>slot_date</t>
         </is>
       </c>
       <c r="D25" s="26" t="inlineStr">
@@ -8766,7 +8901,7 @@
       </c>
       <c r="E25" s="26" t="inlineStr">
         <is>
-          <t>ユーザー別予約一覧</t>
+          <t>日付別予約枠検索</t>
         </is>
       </c>
     </row>
@@ -8778,12 +8913,12 @@
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>idx_appt_pet</t>
+          <t>idx_appt_user</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>pet_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D26" s="26" t="inlineStr">
@@ -8793,7 +8928,7 @@
       </c>
       <c r="E26" s="26" t="inlineStr">
         <is>
-          <t>ペット別予約履歴</t>
+          <t>ユーザー別予約一覧</t>
         </is>
       </c>
     </row>
@@ -8805,12 +8940,12 @@
       </c>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t>idx_appt_slot</t>
+          <t>idx_appt_pet</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>slot_id</t>
+          <t>pet_id</t>
         </is>
       </c>
       <c r="D27" s="26" t="inlineStr">
@@ -8820,7 +8955,7 @@
       </c>
       <c r="E27" s="26" t="inlineStr">
         <is>
-          <t>枠別予約数カウント</t>
+          <t>ペット別予約履歴</t>
         </is>
       </c>
     </row>
@@ -8832,12 +8967,12 @@
       </c>
       <c r="B28" s="26" t="inlineStr">
         <is>
-          <t>idx_appt_date</t>
+          <t>idx_appt_slot</t>
         </is>
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>appointment_date</t>
+          <t>slot_id</t>
         </is>
       </c>
       <c r="D28" s="26" t="inlineStr">
@@ -8847,78 +8982,78 @@
       </c>
       <c r="E28" s="26" t="inlineStr">
         <is>
-          <t>日付別予約一覧（カレンダー表示）</t>
+          <t>枠別予約数カウント</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26" t="inlineStr">
-        <is>
-          <t>medical_histories</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="inlineStr">
-        <is>
-          <t>idx_mh_pet</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>pet_id</t>
-        </is>
-      </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>appointments</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>idx_appointments_slot_id</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>slot_id</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>INDEX</t>
         </is>
       </c>
-      <c r="E29" s="26" t="inlineStr">
-        <is>
-          <t>ペット別診療記録一覧</t>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>予約枠に紐づく予約の高速取得・FK結合</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>medical_histories</t>
+          <t>appointments</t>
         </is>
       </c>
       <c r="B30" s="26" t="inlineStr">
         <is>
-          <t>idx_mh_appt</t>
+          <t>idx_appt_date</t>
         </is>
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>appointment_id</t>
+          <t>appointment_date</t>
         </is>
       </c>
       <c r="D30" s="26" t="inlineStr">
         <is>
-          <t>UNIQUE</t>
+          <t>INDEX</t>
         </is>
       </c>
       <c r="E30" s="26" t="inlineStr">
         <is>
-          <t>予約との1:1整合性保証</t>
+          <t>日付別予約一覧（カレンダー表示）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>medical_attachments</t>
+          <t>medical_histories</t>
         </is>
       </c>
       <c r="B31" s="26" t="inlineStr">
         <is>
-          <t>idx_ma_mh</t>
+          <t>idx_mh_pet</t>
         </is>
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>medical_history_id</t>
+          <t>pet_id</t>
         </is>
       </c>
       <c r="D31" s="26" t="inlineStr">
@@ -8928,35 +9063,51 @@
       </c>
       <c r="E31" s="26" t="inlineStr">
         <is>
-          <t>診療記録別添付ファイル検索</t>
+          <t>ペット別診療記録一覧</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>── メッセージング・通知 ──</t>
-        </is>
-      </c>
-      <c r="B32" s="29" t="n"/>
-      <c r="C32" s="29" t="n"/>
-      <c r="D32" s="29" t="n"/>
-      <c r="E32" s="30" t="n"/>
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>medical_histories</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="inlineStr">
+        <is>
+          <t>idx_mh_appt</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>appointment_id</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="inlineStr">
+        <is>
+          <t>予約との1:1整合性保証</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>consult_chat_messages</t>
+          <t>medical_attachments</t>
         </is>
       </c>
       <c r="B33" s="26" t="inlineStr">
         <is>
-          <t>idx_ccm_user</t>
+          <t>idx_ma_mh</t>
         </is>
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>medical_history_id</t>
         </is>
       </c>
       <c r="D33" s="26" t="inlineStr">
@@ -8966,46 +9117,30 @@
       </c>
       <c r="E33" s="26" t="inlineStr">
         <is>
-          <t>ユーザー別チャット履歴</t>
+          <t>診療記録別添付ファイル検索</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="inlineStr">
-        <is>
-          <t>notifications</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="inlineStr">
-        <is>
-          <t>idx_notif_type</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="D34" s="26" t="inlineStr">
-        <is>
-          <t>INDEX</t>
-        </is>
-      </c>
-      <c r="E34" s="26" t="inlineStr">
-        <is>
-          <t>通知種別フィルター</t>
-        </is>
-      </c>
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>── メッセージング・通知 ──</t>
+        </is>
+      </c>
+      <c r="B34" s="29" t="n"/>
+      <c r="C34" s="29" t="n"/>
+      <c r="D34" s="29" t="n"/>
+      <c r="E34" s="30" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>notification_recipients</t>
+          <t>consult_chat_messages</t>
         </is>
       </c>
       <c r="B35" s="26" t="inlineStr">
         <is>
-          <t>idx_nr_user</t>
+          <t>idx_ccm_user</t>
         </is>
       </c>
       <c r="C35" s="26" t="inlineStr">
@@ -9020,24 +9155,24 @@
       </c>
       <c r="E35" s="26" t="inlineStr">
         <is>
-          <t>ユーザー別未読通知検索</t>
+          <t>ユーザー別チャット履歴</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>notification_recipients</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="B36" s="26" t="inlineStr">
         <is>
-          <t>idx_nr_read</t>
+          <t>idx_notif_type</t>
         </is>
       </c>
       <c r="C36" s="26" t="inlineStr">
         <is>
-          <t>user_id, is_read</t>
+          <t>type</t>
         </is>
       </c>
       <c r="D36" s="26" t="inlineStr">
@@ -9047,51 +9182,51 @@
       </c>
       <c r="E36" s="26" t="inlineStr">
         <is>
-          <t>未読フィルター最適化</t>
+          <t>通知種別フィルター</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>email_templates</t>
+          <t>notification_recipients</t>
         </is>
       </c>
       <c r="B37" s="26" t="inlineStr">
         <is>
-          <t>uk_et_code</t>
+          <t>idx_nr_user</t>
         </is>
       </c>
       <c r="C37" s="26" t="inlineStr">
         <is>
-          <t>template_code</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D37" s="26" t="inlineStr">
         <is>
-          <t>UNIQUE</t>
+          <t>INDEX</t>
         </is>
       </c>
       <c r="E37" s="26" t="inlineStr">
         <is>
-          <t>テンプレートコードの一意性確保</t>
+          <t>ユーザー別未読通知検索</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>email_messages</t>
+          <t>notification_recipients</t>
         </is>
       </c>
       <c r="B38" s="26" t="inlineStr">
         <is>
-          <t>idx_em_status</t>
+          <t>idx_nr_read</t>
         </is>
       </c>
       <c r="C38" s="26" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>user_id, is_read</t>
         </is>
       </c>
       <c r="D38" s="26" t="inlineStr">
@@ -9101,62 +9236,78 @@
       </c>
       <c r="E38" s="26" t="inlineStr">
         <is>
-          <t>送信待ちキュー処理</t>
+          <t>未読フィルター最適化</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="26" t="inlineStr">
         <is>
+          <t>email_templates</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>uk_et_code</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>template_code</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
+      <c r="E39" s="26" t="inlineStr">
+        <is>
+          <t>テンプレートコードの一意性確保</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
           <t>email_messages</t>
         </is>
       </c>
-      <c r="B39" s="26" t="inlineStr">
-        <is>
-          <t>idx_em_template</t>
-        </is>
-      </c>
-      <c r="C39" s="26" t="inlineStr">
-        <is>
-          <t>template_id</t>
-        </is>
-      </c>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="B40" s="26" t="inlineStr">
+        <is>
+          <t>idx_em_status</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
         <is>
           <t>INDEX</t>
         </is>
       </c>
-      <c r="E39" s="26" t="inlineStr">
-        <is>
-          <t>テンプレート別送信履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="28" t="inlineStr">
-        <is>
-          <t>── UX補助 ──</t>
-        </is>
-      </c>
-      <c r="B40" s="29" t="n"/>
-      <c r="C40" s="29" t="n"/>
-      <c r="D40" s="29" t="n"/>
-      <c r="E40" s="30" t="n"/>
+      <c r="E40" s="26" t="inlineStr">
+        <is>
+          <t>送信待ちキュー処理</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>pet_calendar_marks</t>
+          <t>email_messages</t>
         </is>
       </c>
       <c r="B41" s="26" t="inlineStr">
         <is>
-          <t>idx_pcm_pet_date</t>
+          <t>idx_em_template</t>
         </is>
       </c>
       <c r="C41" s="26" t="inlineStr">
         <is>
-          <t>pet_id, mark_date</t>
+          <t>template_id</t>
         </is>
       </c>
       <c r="D41" s="26" t="inlineStr">
@@ -9166,51 +9317,35 @@
       </c>
       <c r="E41" s="26" t="inlineStr">
         <is>
-          <t>ペット別カレンダーマーク検索</t>
+          <t>テンプレート別送信履歴</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="26" t="inlineStr">
-        <is>
-          <t>dismissed_reminders</t>
-        </is>
-      </c>
-      <c r="B42" s="26" t="inlineStr">
-        <is>
-          <t>uk_dr_user_key</t>
-        </is>
-      </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>user_id, reminder_key</t>
-        </is>
-      </c>
-      <c r="D42" s="26" t="inlineStr">
-        <is>
-          <t>UNIQUE</t>
-        </is>
-      </c>
-      <c r="E42" s="26" t="inlineStr">
-        <is>
-          <t>ユーザー別リマインダー重複防止</t>
-        </is>
-      </c>
+      <c r="A42" s="28" t="inlineStr">
+        <is>
+          <t>── UX補助 ──</t>
+        </is>
+      </c>
+      <c r="B42" s="29" t="n"/>
+      <c r="C42" s="29" t="n"/>
+      <c r="D42" s="29" t="n"/>
+      <c r="E42" s="30" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>announcements</t>
+          <t>pet_calendar_marks</t>
         </is>
       </c>
       <c r="B43" s="26" t="inlineStr">
         <is>
-          <t>idx_ann_published</t>
+          <t>idx_pcm_pet_date</t>
         </is>
       </c>
       <c r="C43" s="26" t="inlineStr">
         <is>
-          <t>published_at</t>
+          <t>pet_id, mark_date</t>
         </is>
       </c>
       <c r="D43" s="26" t="inlineStr">
@@ -9220,24 +9355,24 @@
       </c>
       <c r="E43" s="26" t="inlineStr">
         <is>
-          <t>公開日時順ソート</t>
+          <t>ペット別カレンダーマーク検索</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>password_reset_tokens</t>
+          <t>dismissed_reminders</t>
         </is>
       </c>
       <c r="B44" s="26" t="inlineStr">
         <is>
-          <t>uk_prt_token</t>
+          <t>uk_dr_user_key</t>
         </is>
       </c>
       <c r="C44" s="26" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>user_id, reminder_key</t>
         </is>
       </c>
       <c r="D44" s="26" t="inlineStr">
@@ -9247,32 +9382,86 @@
       </c>
       <c r="E44" s="26" t="inlineStr">
         <is>
-          <t>トークンの一意性確保</t>
+          <t>ユーザー別リマインダー重複防止</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="26" t="inlineStr">
         <is>
+          <t>announcements</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="inlineStr">
+        <is>
+          <t>idx_ann_published</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>published_at</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
+        <is>
+          <t>INDEX</t>
+        </is>
+      </c>
+      <c r="E45" s="26" t="inlineStr">
+        <is>
+          <t>公開日時順ソート</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
           <t>password_reset_tokens</t>
         </is>
       </c>
-      <c r="B45" s="26" t="inlineStr">
+      <c r="B46" s="26" t="inlineStr">
+        <is>
+          <t>uk_prt_token</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
+        <is>
+          <t>トークンの一意性確保</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>password_reset_tokens</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="inlineStr">
         <is>
           <t>idx_prt_user</t>
         </is>
       </c>
-      <c r="C45" s="26" t="inlineStr">
+      <c r="C47" s="26" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="D45" s="26" t="inlineStr">
+      <c r="D47" s="26" t="inlineStr">
         <is>
           <t>INDEX</t>
         </is>
       </c>
-      <c r="E45" s="26" t="inlineStr">
+      <c r="E47" s="26" t="inlineStr">
         <is>
           <t>ユーザー別トークン検索</t>
         </is>
@@ -9575,7 +9764,7 @@
     <row r="20" ht="15" customHeight="1" s="12">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>users（DataInitializerが BCrypt ハッシュで作成）</t>
+          <t>users（通常は data.sql で投入。DataInitializer は data.sql 無効時のみ BCrypt でフォールバック作成）</t>
         </is>
       </c>
     </row>
@@ -9850,12 +10039,12 @@
       </c>
       <c r="B37" s="26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C37" s="26" t="inlineStr">
         <is>
-          <t>owner1→ポチ(STANDARD)、owner2→レオン(STANDARD)、owner1→ピーコ(LIGHT)、owner2→カレン(STANDARD)、owner3→ボス(PREMIUM)</t>
+          <t>owner1→ピーコ(LIGHT)、owner2→カレン(STANDARD)、owner3→ボス(PREMIUM)</t>
         </is>
       </c>
       <c r="D37" s="26" t="inlineStr"/>
